--- a/00_Data/DF EOF Site & Year Metadata (2004-2023).xlsx
+++ b/00_Data/DF EOF Site & Year Metadata (2004-2023).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwprod-my.sharepoint.com/personal/zchen2545_wisc_edu/Documents/Research/Discovery Farms/DF Programs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwprod-my.sharepoint.com/personal/zchen2545_wisc_edu/Documents/Research/Discovery Farms/DF Runoff Generation/Github repo/DF_runoff/00_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{B78423C8-A332-48E0-B5C7-5F938FB9312B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AE56553-5712-4CF2-A46F-9AB43EF8BA70}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{B78423C8-A332-48E0-B5C7-5F938FB9312B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2B78396-9E5D-44A0-9E80-6EDE0BBE8160}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="1272" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="1272" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site" sheetId="1" r:id="rId1"/>
@@ -1561,7 +1561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1571,6 +1571,7 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1595,7 +1596,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1611,6 +1612,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1904,39 +1909,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="11" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="13" t="s">
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="14" t="s">
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="9" t="s">
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="W1" s="10"/>
+      <c r="W1" s="11"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -4449,144 +4454,144 @@
       <c r="W37" s="1"/>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="9" t="s">
         <v>384</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="D38" s="17">
+      <c r="D38" s="9">
         <v>5</v>
       </c>
-      <c r="E38" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="17" t="s">
+      <c r="E38" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H38" s="17" t="s">
+      <c r="H38" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I38" s="17">
+      <c r="I38" s="9">
         <v>44.401277780000001</v>
       </c>
-      <c r="J38" s="17">
+      <c r="J38" s="9">
         <v>-87.695555600000006</v>
       </c>
-      <c r="K38" s="17" t="s">
+      <c r="K38" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L38" s="17" t="s">
+      <c r="L38" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="M38" s="17" t="s">
+      <c r="M38" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="N38" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="O38" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="P38" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q38" s="17">
+      <c r="N38" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="O38" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P38" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q38" s="9">
         <v>2.63</v>
       </c>
-      <c r="R38" s="17" t="s">
+      <c r="R38" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="S38" s="17" t="s">
+      <c r="S38" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="T38" s="17" t="s">
+      <c r="T38" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="U38" s="17">
+      <c r="U38" s="9">
         <v>3.92</v>
       </c>
-      <c r="V38" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="W38" s="17" t="s">
+      <c r="V38" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="W38" s="9" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="9" t="s">
         <v>367</v>
       </c>
-      <c r="D39" s="17">
+      <c r="D39" s="9">
         <v>5</v>
       </c>
-      <c r="E39" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="17" t="s">
+      <c r="E39" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H39" s="17" t="s">
+      <c r="H39" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I39" s="17">
+      <c r="I39" s="9">
         <v>44.36527778</v>
       </c>
-      <c r="J39" s="17">
+      <c r="J39" s="9">
         <v>-87.549888890000005</v>
       </c>
-      <c r="K39" s="17" t="s">
+      <c r="K39" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="L39" s="17" t="s">
+      <c r="L39" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="M39" s="17" t="s">
+      <c r="M39" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="N39" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="O39" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="P39" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q39" s="17">
+      <c r="N39" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="O39" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P39" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q39" s="9">
         <v>19.8</v>
       </c>
-      <c r="R39" s="17" t="s">
+      <c r="R39" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="S39" s="17" t="s">
+      <c r="S39" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="T39" s="17" t="s">
+      <c r="T39" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="U39" s="17">
+      <c r="U39" s="9">
         <v>3.96</v>
       </c>
-      <c r="V39" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="W39" s="17" t="s">
+      <c r="V39" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="W39" s="9" t="s">
         <v>387</v>
       </c>
     </row>
@@ -5119,22 +5124,22 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D3">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="E3" t="s">
         <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H3" t="s">
         <v>90</v>
@@ -5146,7 +5151,7 @@
         <v>90</v>
       </c>
       <c r="K3" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="L3" t="s">
         <v>45</v>
@@ -5157,22 +5162,22 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D4">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="E4" t="s">
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H4" t="s">
         <v>90</v>
@@ -5184,97 +5189,97 @@
         <v>90</v>
       </c>
       <c r="K4" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="L4" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="D5">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="E5" t="s">
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H5" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I5" t="s">
         <v>29</v>
       </c>
       <c r="J5" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K5" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L5" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="D6">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H6" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I6" t="s">
         <v>29</v>
       </c>
       <c r="J6" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K6" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L6" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="D7">
         <v>2004</v>
@@ -5286,22 +5291,22 @@
         <v>73</v>
       </c>
       <c r="G7" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H7" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I7" t="s">
         <v>29</v>
       </c>
       <c r="J7" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="L7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -5309,10 +5314,10 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D8">
         <v>2005</v>
@@ -5321,7 +5326,7 @@
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
         <v>80</v>
@@ -5347,13 +5352,13 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="E9" t="s">
         <v>26</v>
@@ -5377,7 +5382,7 @@
         <v>81</v>
       </c>
       <c r="L9" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -5385,13 +5390,13 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
         <v>55</v>
       </c>
       <c r="D10">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="E10" t="s">
         <v>26</v>
@@ -5400,7 +5405,7 @@
         <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H10" t="s">
         <v>90</v>
@@ -5412,7 +5417,7 @@
         <v>90</v>
       </c>
       <c r="K10" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="L10" t="s">
         <v>45</v>
@@ -5423,19 +5428,19 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D11">
         <v>2005</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
         <v>80</v>
@@ -5461,16 +5466,16 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D12">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F12" t="s">
         <v>25</v>
@@ -5491,141 +5496,141 @@
         <v>81</v>
       </c>
       <c r="L12" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="D13">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="E13" t="s">
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H13" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I13" t="s">
         <v>29</v>
       </c>
       <c r="J13" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K13" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="L13" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="D14">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="E14" t="s">
         <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I14" t="s">
         <v>29</v>
       </c>
       <c r="J14" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K14" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="L14" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="D15">
         <v>2005</v>
       </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H15" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I15" t="s">
         <v>29</v>
       </c>
       <c r="J15" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K15" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L15" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="D16">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G16" t="s">
         <v>80</v>
@@ -5640,30 +5645,30 @@
         <v>90</v>
       </c>
       <c r="K16" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="L16" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>22</v>
+      <c r="A17" s="18" t="s">
+        <v>150</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>177</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>154</v>
       </c>
       <c r="D17">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G17" t="s">
         <v>80</v>
@@ -5678,36 +5683,36 @@
         <v>90</v>
       </c>
       <c r="K17" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L17" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>22</v>
+      <c r="A18" s="18" t="s">
+        <v>150</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>179</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>155</v>
       </c>
       <c r="D18">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="H18" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I18" t="s">
         <v>29</v>
@@ -5716,10 +5721,10 @@
         <v>90</v>
       </c>
       <c r="K18" t="s">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s">
-        <v>81</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
@@ -5727,19 +5732,19 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="D19">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="E19" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G19" t="s">
         <v>80</v>
@@ -5757,7 +5762,7 @@
         <v>81</v>
       </c>
       <c r="L19" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -5765,19 +5770,19 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="D20">
         <v>2006</v>
       </c>
       <c r="E20" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G20" t="s">
         <v>80</v>
@@ -5803,16 +5808,16 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D21">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="E21" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
         <v>25</v>
@@ -5841,19 +5846,19 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D22">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G22" t="s">
         <v>80</v>
@@ -5876,40 +5881,40 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="D23">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="E23" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G23" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s">
         <v>29</v>
       </c>
       <c r="J23" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L23" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
@@ -5917,13 +5922,13 @@
         <v>82</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
         <v>83</v>
       </c>
       <c r="D24">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="E24" t="s">
         <v>26</v>
@@ -5944,10 +5949,10 @@
         <v>176</v>
       </c>
       <c r="K24" t="s">
+        <v>47</v>
+      </c>
+      <c r="L24" t="s">
         <v>115</v>
-      </c>
-      <c r="L24" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
@@ -5955,10 +5960,10 @@
         <v>82</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D25">
         <v>2006</v>
@@ -5993,13 +5998,13 @@
         <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D26">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="E26" t="s">
         <v>26</v>
@@ -6028,16 +6033,16 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="D27">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="E27" t="s">
         <v>26</v>
@@ -6046,39 +6051,39 @@
         <v>73</v>
       </c>
       <c r="G27" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s">
         <v>29</v>
       </c>
       <c r="J27" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="L27" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>82</v>
+      <c r="A28" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>129</v>
       </c>
       <c r="D28">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="E28" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F28" t="s">
         <v>73</v>
@@ -6096,27 +6101,27 @@
         <v>176</v>
       </c>
       <c r="K28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L28" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>82</v>
+      <c r="A29" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="D29">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="E29" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F29" t="s">
         <v>73</v>
@@ -6141,17 +6146,17 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>82</v>
+      <c r="A30" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="D30">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="E30" t="s">
         <v>26</v>
@@ -6179,17 +6184,17 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>82</v>
+      <c r="A31" s="18" t="s">
+        <v>150</v>
       </c>
       <c r="B31" t="s">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="D31">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="E31" t="s">
         <v>26</v>
@@ -6198,45 +6203,45 @@
         <v>73</v>
       </c>
       <c r="G31" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H31" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I31" t="s">
         <v>29</v>
       </c>
       <c r="J31" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="L31" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>82</v>
+      <c r="A32" s="18" t="s">
+        <v>150</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>180</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="D32">
         <v>2006</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F32" t="s">
         <v>73</v>
       </c>
       <c r="G32" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="H32" t="s">
         <v>29</v>
@@ -6245,24 +6250,24 @@
         <v>29</v>
       </c>
       <c r="J32" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="L32" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="D33">
         <v>2007</v>
@@ -6271,139 +6276,139 @@
         <v>26</v>
       </c>
       <c r="F33" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G33" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I33" t="s">
         <v>29</v>
       </c>
       <c r="J33" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L33" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="D34">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="E34" t="s">
         <v>26</v>
       </c>
       <c r="F34" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G34" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s">
         <v>29</v>
       </c>
       <c r="J34" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="L34" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D35">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F35" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G35" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I35" t="s">
         <v>29</v>
       </c>
       <c r="J35" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L35" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="C36" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D36">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E36" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F36" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G36" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s">
         <v>29</v>
       </c>
       <c r="J36" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K36" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L36" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -6411,13 +6416,13 @@
         <v>82</v>
       </c>
       <c r="B37" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C37" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D37">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="E37" t="s">
         <v>26</v>
@@ -6438,7 +6443,7 @@
         <v>176</v>
       </c>
       <c r="K37" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="L37" t="s">
         <v>47</v>
@@ -6449,13 +6454,13 @@
         <v>82</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D38">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="E38" t="s">
         <v>26</v>
@@ -6479,7 +6484,7 @@
         <v>47</v>
       </c>
       <c r="L38" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -6487,13 +6492,13 @@
         <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
         <v>85</v>
       </c>
       <c r="D39">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="E39" t="s">
         <v>26</v>
@@ -6514,7 +6519,7 @@
         <v>176</v>
       </c>
       <c r="K39" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="L39" t="s">
         <v>47</v>
@@ -6522,13 +6527,13 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="D40">
         <v>2007</v>
@@ -6540,39 +6545,39 @@
         <v>73</v>
       </c>
       <c r="G40" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I40" t="s">
         <v>29</v>
       </c>
       <c r="J40" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K40" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="L40" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>82</v>
+      <c r="A41" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C41" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="D41">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="E41" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F41" t="s">
         <v>73</v>
@@ -6593,24 +6598,24 @@
         <v>47</v>
       </c>
       <c r="L41" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>82</v>
+      <c r="A42" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>145</v>
       </c>
       <c r="C42" t="s">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="D42">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="E42" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F42" t="s">
         <v>73</v>
@@ -6628,24 +6633,24 @@
         <v>176</v>
       </c>
       <c r="K42" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="L42" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>82</v>
+      <c r="A43" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="D43">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E43" t="s">
         <v>26</v>
@@ -6673,29 +6678,29 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>117</v>
+      <c r="A44" s="18" t="s">
+        <v>150</v>
       </c>
       <c r="B44" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="C44" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="D44">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="E44" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F44" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G44" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="H44" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I44" t="s">
         <v>29</v>
@@ -6704,30 +6709,30 @@
         <v>90</v>
       </c>
       <c r="K44" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="L44" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>117</v>
+        <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="D45">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="E45" t="s">
         <v>26</v>
       </c>
       <c r="F45" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G45" t="s">
         <v>80</v>
@@ -6742,30 +6747,30 @@
         <v>90</v>
       </c>
       <c r="K45" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="L45" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>59</v>
       </c>
       <c r="C46" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
       <c r="D46">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E46" t="s">
         <v>26</v>
       </c>
       <c r="F46" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G46" t="s">
         <v>80</v>
@@ -6780,103 +6785,103 @@
         <v>90</v>
       </c>
       <c r="K46" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="L46" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>64</v>
       </c>
       <c r="C47" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="D47">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G47" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H47" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I47" t="s">
         <v>29</v>
       </c>
       <c r="J47" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="L47" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>127</v>
+        <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>69</v>
       </c>
       <c r="C48" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="D48">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
       </c>
       <c r="F48" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G48" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I48" t="s">
         <v>29</v>
       </c>
       <c r="J48" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L48" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="B49" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="C49" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="D49">
         <v>2008</v>
       </c>
       <c r="E49" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F49" t="s">
         <v>73</v>
@@ -6894,7 +6899,7 @@
         <v>176</v>
       </c>
       <c r="K49" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="L49" t="s">
         <v>47</v>
@@ -6902,19 +6907,19 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="B50" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="C50" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="D50">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="E50" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F50" t="s">
         <v>73</v>
@@ -6932,7 +6937,7 @@
         <v>176</v>
       </c>
       <c r="K50" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="L50" t="s">
         <v>47</v>
@@ -6940,19 +6945,19 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="C51" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="D51">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E51" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F51" t="s">
         <v>73</v>
@@ -6970,10 +6975,10 @@
         <v>176</v>
       </c>
       <c r="K51" t="s">
+        <v>47</v>
+      </c>
+      <c r="L51" t="s">
         <v>115</v>
-      </c>
-      <c r="L51" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
@@ -6981,10 +6986,10 @@
         <v>127</v>
       </c>
       <c r="B52" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C52" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D52">
         <v>2008</v>
@@ -7011,7 +7016,7 @@
         <v>47</v>
       </c>
       <c r="L52" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -7019,16 +7024,16 @@
         <v>127</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D53">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="E53" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F53" t="s">
         <v>73</v>
@@ -7049,7 +7054,7 @@
         <v>47</v>
       </c>
       <c r="L53" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -7057,13 +7062,13 @@
         <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C54" t="s">
         <v>128</v>
       </c>
       <c r="D54">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E54" t="s">
         <v>26</v>
@@ -7084,21 +7089,21 @@
         <v>176</v>
       </c>
       <c r="K54" t="s">
+        <v>47</v>
+      </c>
+      <c r="L54" t="s">
         <v>115</v>
-      </c>
-      <c r="L54" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="B55" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="C55" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="D55">
         <v>2008</v>
@@ -7107,10 +7112,10 @@
         <v>26</v>
       </c>
       <c r="F55" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G55" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="H55" t="s">
         <v>29</v>
@@ -7119,13 +7124,13 @@
         <v>29</v>
       </c>
       <c r="J55" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K55" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="L55" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
@@ -7133,25 +7138,25 @@
         <v>150</v>
       </c>
       <c r="B56" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C56" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D56">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="E56" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F56" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G56" t="s">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="H56" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I56" t="s">
         <v>29</v>
@@ -7160,10 +7165,10 @@
         <v>90</v>
       </c>
       <c r="K56" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="L56" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -7171,13 +7176,13 @@
         <v>150</v>
       </c>
       <c r="B57" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="C57" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D57">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="E57" t="s">
         <v>26</v>
@@ -7186,10 +7191,10 @@
         <v>73</v>
       </c>
       <c r="G57" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="H57" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I57" t="s">
         <v>29</v>
@@ -7198,10 +7203,10 @@
         <v>90</v>
       </c>
       <c r="K57" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="L57" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -7209,16 +7214,16 @@
         <v>150</v>
       </c>
       <c r="B58" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="C58" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D58">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="E58" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F58" t="s">
         <v>73</v>
@@ -7244,25 +7249,25 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>180</v>
+        <v>98</v>
       </c>
       <c r="C59" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="D59">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="E59" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F59" t="s">
         <v>73</v>
       </c>
       <c r="G59" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="H59" t="s">
         <v>29</v>
@@ -7271,36 +7276,36 @@
         <v>29</v>
       </c>
       <c r="J59" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K59" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="L59" t="s">
-        <v>197</v>
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="B60" t="s">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="C60" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="D60">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="E60" t="s">
         <v>26</v>
       </c>
       <c r="F60" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G60" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="H60" t="s">
         <v>29</v>
@@ -7309,24 +7314,24 @@
         <v>29</v>
       </c>
       <c r="J60" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K60" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="L60" t="s">
-        <v>197</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="B61" t="s">
-        <v>182</v>
+        <v>112</v>
       </c>
       <c r="C61" t="s">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="D61">
         <v>2009</v>
@@ -7335,10 +7340,10 @@
         <v>26</v>
       </c>
       <c r="F61" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G61" t="s">
-        <v>198</v>
+        <v>114</v>
       </c>
       <c r="H61" t="s">
         <v>29</v>
@@ -7347,13 +7352,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K61" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="L61" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
@@ -7361,13 +7366,13 @@
         <v>150</v>
       </c>
       <c r="B62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C62" t="s">
         <v>156</v>
       </c>
       <c r="D62">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="E62" t="s">
         <v>26</v>
@@ -7399,22 +7404,22 @@
         <v>150</v>
       </c>
       <c r="B63" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C63" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D63">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="E63" t="s">
         <v>26</v>
       </c>
       <c r="F63" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G63" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H63" t="s">
         <v>29</v>
@@ -7437,19 +7442,19 @@
         <v>150</v>
       </c>
       <c r="B64" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="C64" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D64">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="E64" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F64" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G64" t="s">
         <v>197</v>
@@ -7472,25 +7477,25 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="B65" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="C65" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="D65">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="E65" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F65" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G65" t="s">
-        <v>198</v>
+        <v>114</v>
       </c>
       <c r="H65" t="s">
         <v>29</v>
@@ -7499,36 +7504,36 @@
         <v>29</v>
       </c>
       <c r="J65" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K65" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="L65" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="B66" t="s">
-        <v>187</v>
+        <v>106</v>
       </c>
       <c r="C66" t="s">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="D66">
         <v>2010</v>
       </c>
       <c r="E66" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F66" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G66" t="s">
-        <v>198</v>
+        <v>114</v>
       </c>
       <c r="H66" t="s">
         <v>29</v>
@@ -7537,36 +7542,36 @@
         <v>29</v>
       </c>
       <c r="J66" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K66" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="L66" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="B67" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="C67" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="D67">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E67" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F67" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G67" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="H67" t="s">
         <v>29</v>
@@ -7575,13 +7580,13 @@
         <v>29</v>
       </c>
       <c r="J67" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K67" t="s">
-        <v>197</v>
+        <v>115</v>
       </c>
       <c r="L67" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
@@ -7589,22 +7594,22 @@
         <v>150</v>
       </c>
       <c r="B68" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C68" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D68">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="E68" t="s">
         <v>26</v>
       </c>
       <c r="F68" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G68" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H68" t="s">
         <v>29</v>
@@ -7627,19 +7632,19 @@
         <v>150</v>
       </c>
       <c r="B69" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C69" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D69">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="E69" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F69" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G69" t="s">
         <v>198</v>
@@ -7703,13 +7708,13 @@
         <v>150</v>
       </c>
       <c r="B71" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C71" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D71">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E71" t="s">
         <v>26</v>
@@ -7718,7 +7723,7 @@
         <v>73</v>
       </c>
       <c r="G71" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H71" t="s">
         <v>29</v>
@@ -7741,19 +7746,19 @@
         <v>150</v>
       </c>
       <c r="B72" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C72" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D72">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="E72" t="s">
         <v>26</v>
       </c>
       <c r="F72" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G72" t="s">
         <v>197</v>
@@ -7779,19 +7784,19 @@
         <v>150</v>
       </c>
       <c r="B73" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C73" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D73">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="E73" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F73" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G73" t="s">
         <v>197</v>
@@ -7817,13 +7822,13 @@
         <v>150</v>
       </c>
       <c r="B74" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C74" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D74">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="E74" t="s">
         <v>26</v>
@@ -7832,7 +7837,7 @@
         <v>73</v>
       </c>
       <c r="G74" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H74" t="s">
         <v>29</v>
@@ -7931,13 +7936,13 @@
         <v>199</v>
       </c>
       <c r="B77" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C77" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D77">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E77" t="s">
         <v>26</v>
@@ -7946,7 +7951,7 @@
         <v>73</v>
       </c>
       <c r="G77" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="H77" t="s">
         <v>29</v>
@@ -7958,10 +7963,10 @@
         <v>90</v>
       </c>
       <c r="K77" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="L77" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
@@ -7969,13 +7974,13 @@
         <v>199</v>
       </c>
       <c r="B78" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C78" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D78">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="E78" t="s">
         <v>26</v>
@@ -7984,22 +7989,22 @@
         <v>73</v>
       </c>
       <c r="G78" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="H78" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="I78" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J78" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K78" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="L78" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
@@ -8007,13 +8012,13 @@
         <v>199</v>
       </c>
       <c r="B79" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="C79" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D79">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="E79" t="s">
         <v>26</v>
@@ -8022,10 +8027,10 @@
         <v>73</v>
       </c>
       <c r="G79" t="s">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="H79" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I79" t="s">
         <v>29</v>
@@ -8037,7 +8042,7 @@
         <v>126</v>
       </c>
       <c r="L79" t="s">
-        <v>126</v>
+        <v>262</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
@@ -8045,13 +8050,13 @@
         <v>199</v>
       </c>
       <c r="B80" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="C80" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D80">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="E80" t="s">
         <v>26</v>
@@ -8060,10 +8065,10 @@
         <v>73</v>
       </c>
       <c r="G80" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H80" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I80" t="s">
         <v>29</v>
@@ -8075,21 +8080,21 @@
         <v>126</v>
       </c>
       <c r="L80" t="s">
-        <v>126</v>
+        <v>262</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="B81" t="s">
-        <v>226</v>
+        <v>276</v>
       </c>
       <c r="C81" t="s">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="D81">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="E81" t="s">
         <v>26</v>
@@ -8098,33 +8103,33 @@
         <v>73</v>
       </c>
       <c r="G81" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I81" t="s">
         <v>29</v>
       </c>
       <c r="J81" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K81" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="L81" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="B82" t="s">
-        <v>227</v>
+        <v>283</v>
       </c>
       <c r="C82" t="s">
-        <v>201</v>
+        <v>284</v>
       </c>
       <c r="D82">
         <v>2011</v>
@@ -8136,10 +8141,10 @@
         <v>73</v>
       </c>
       <c r="G82" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="H82" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I82" t="s">
         <v>29</v>
@@ -8148,10 +8153,10 @@
         <v>90</v>
       </c>
       <c r="K82" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="L82" t="s">
-        <v>197</v>
+        <v>115</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
@@ -8159,10 +8164,10 @@
         <v>199</v>
       </c>
       <c r="B83" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C83" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D83">
         <v>2012</v>
@@ -8174,7 +8179,7 @@
         <v>73</v>
       </c>
       <c r="G83" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="H83" t="s">
         <v>29</v>
@@ -8186,10 +8191,10 @@
         <v>90</v>
       </c>
       <c r="K83" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="L83" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
@@ -8197,13 +8202,13 @@
         <v>199</v>
       </c>
       <c r="B84" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C84" t="s">
         <v>201</v>
       </c>
       <c r="D84">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="E84" t="s">
         <v>26</v>
@@ -8235,13 +8240,13 @@
         <v>199</v>
       </c>
       <c r="B85" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C85" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D85">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="E85" t="s">
         <v>26</v>
@@ -8250,22 +8255,22 @@
         <v>73</v>
       </c>
       <c r="G85" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="H85" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="I85" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J85" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K85" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="L85" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
@@ -8273,13 +8278,13 @@
         <v>199</v>
       </c>
       <c r="B86" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C86" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D86">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="E86" t="s">
         <v>26</v>
@@ -8288,10 +8293,10 @@
         <v>73</v>
       </c>
       <c r="G86" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="H86" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I86" t="s">
         <v>29</v>
@@ -8300,10 +8305,10 @@
         <v>90</v>
       </c>
       <c r="K86" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="L86" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
@@ -8311,13 +8316,13 @@
         <v>199</v>
       </c>
       <c r="B87" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C87" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D87">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="E87" t="s">
         <v>26</v>
@@ -8326,10 +8331,10 @@
         <v>73</v>
       </c>
       <c r="G87" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I87" t="s">
         <v>29</v>
@@ -8338,10 +8343,10 @@
         <v>90</v>
       </c>
       <c r="K87" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="L87" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
@@ -8349,13 +8354,13 @@
         <v>199</v>
       </c>
       <c r="B88" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="C88" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D88">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E88" t="s">
         <v>26</v>
@@ -8384,13 +8389,13 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="B89" t="s">
-        <v>234</v>
+        <v>278</v>
       </c>
       <c r="C89" t="s">
-        <v>202</v>
+        <v>277</v>
       </c>
       <c r="D89">
         <v>2012</v>
@@ -8402,36 +8407,36 @@
         <v>73</v>
       </c>
       <c r="G89" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I89" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J89" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="K89" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="L89" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="B90" t="s">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="C90" t="s">
-        <v>202</v>
+        <v>284</v>
       </c>
       <c r="D90">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="E90" t="s">
         <v>26</v>
@@ -8440,22 +8445,22 @@
         <v>73</v>
       </c>
       <c r="G90" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H90" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I90" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J90" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K90" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="L90" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
@@ -8463,13 +8468,13 @@
         <v>199</v>
       </c>
       <c r="B91" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="C91" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D91">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="E91" t="s">
         <v>26</v>
@@ -8478,22 +8483,22 @@
         <v>73</v>
       </c>
       <c r="G91" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="H91" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I91" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J91" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K91" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="L91" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
@@ -8501,13 +8506,13 @@
         <v>199</v>
       </c>
       <c r="B92" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C92" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D92">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="E92" t="s">
         <v>26</v>
@@ -8516,22 +8521,22 @@
         <v>73</v>
       </c>
       <c r="G92" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="H92" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I92" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J92" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K92" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="L92" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
@@ -8539,13 +8544,13 @@
         <v>199</v>
       </c>
       <c r="B93" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C93" t="s">
         <v>202</v>
       </c>
       <c r="D93">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="E93" t="s">
         <v>26</v>
@@ -8577,13 +8582,13 @@
         <v>199</v>
       </c>
       <c r="B94" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C94" t="s">
         <v>203</v>
       </c>
       <c r="D94">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="E94" t="s">
         <v>26</v>
@@ -8615,13 +8620,13 @@
         <v>199</v>
       </c>
       <c r="B95" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C95" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D95">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="E95" t="s">
         <v>26</v>
@@ -8630,7 +8635,7 @@
         <v>73</v>
       </c>
       <c r="G95" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s">
         <v>90</v>
@@ -8653,10 +8658,10 @@
         <v>199</v>
       </c>
       <c r="B96" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C96" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D96">
         <v>2013</v>
@@ -8668,36 +8673,36 @@
         <v>73</v>
       </c>
       <c r="G96" t="s">
-        <v>263</v>
+        <v>73</v>
       </c>
       <c r="H96" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I96" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J96" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K96" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="L96" t="s">
-        <v>262</v>
+        <v>73</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="8" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="B97" t="s">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="C97" t="s">
-        <v>203</v>
+        <v>277</v>
       </c>
       <c r="D97">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="E97" t="s">
         <v>26</v>
@@ -8706,7 +8711,7 @@
         <v>73</v>
       </c>
       <c r="G97" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="H97" t="s">
         <v>90</v>
@@ -8715,27 +8720,27 @@
         <v>29</v>
       </c>
       <c r="J97" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K97" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="L97" t="s">
-        <v>262</v>
+        <v>47</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="8" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="B98" t="s">
-        <v>243</v>
+        <v>286</v>
       </c>
       <c r="C98" t="s">
-        <v>203</v>
+        <v>284</v>
       </c>
       <c r="D98">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="E98" t="s">
         <v>26</v>
@@ -8744,7 +8749,7 @@
         <v>73</v>
       </c>
       <c r="G98" t="s">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="H98" t="s">
         <v>90</v>
@@ -8756,10 +8761,10 @@
         <v>90</v>
       </c>
       <c r="K98" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="L98" t="s">
-        <v>262</v>
+        <v>45</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
@@ -8767,13 +8772,13 @@
         <v>199</v>
       </c>
       <c r="B99" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="C99" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D99">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="E99" t="s">
         <v>26</v>
@@ -8782,10 +8787,10 @@
         <v>73</v>
       </c>
       <c r="G99" t="s">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="H99" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I99" t="s">
         <v>29</v>
@@ -8797,7 +8802,7 @@
         <v>126</v>
       </c>
       <c r="L99" t="s">
-        <v>262</v>
+        <v>126</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
@@ -8805,13 +8810,13 @@
         <v>199</v>
       </c>
       <c r="B100" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="C100" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D100">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="E100" t="s">
         <v>26</v>
@@ -8820,10 +8825,10 @@
         <v>73</v>
       </c>
       <c r="G100" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="H100" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I100" t="s">
         <v>29</v>
@@ -8832,10 +8837,10 @@
         <v>90</v>
       </c>
       <c r="K100" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="L100" t="s">
-        <v>262</v>
+        <v>197</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
@@ -8843,13 +8848,13 @@
         <v>199</v>
       </c>
       <c r="B101" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C101" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D101">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="E101" t="s">
         <v>26</v>
@@ -8858,22 +8863,22 @@
         <v>73</v>
       </c>
       <c r="G101" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H101" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I101" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J101" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K101" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="L101" t="s">
-        <v>262</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
@@ -8881,13 +8886,13 @@
         <v>199</v>
       </c>
       <c r="B102" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C102" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D102">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E102" t="s">
         <v>26</v>
@@ -8896,7 +8901,7 @@
         <v>73</v>
       </c>
       <c r="G102" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="H102" t="s">
         <v>90</v>
@@ -8957,13 +8962,13 @@
         <v>199</v>
       </c>
       <c r="B104" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C104" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D104">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="E104" t="s">
         <v>26</v>
@@ -8972,36 +8977,36 @@
         <v>73</v>
       </c>
       <c r="G104" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H104" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I104" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J104" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K104" t="s">
-        <v>126</v>
+        <v>73</v>
       </c>
       <c r="L104" t="s">
-        <v>262</v>
+        <v>73</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="B105" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="C105" t="s">
-        <v>204</v>
+        <v>277</v>
       </c>
       <c r="D105">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="E105" t="s">
         <v>26</v>
@@ -9010,7 +9015,7 @@
         <v>73</v>
       </c>
       <c r="G105" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="H105" t="s">
         <v>90</v>
@@ -9019,27 +9024,27 @@
         <v>29</v>
       </c>
       <c r="J105" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K105" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="L105" t="s">
-        <v>262</v>
+        <v>47</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="B106" t="s">
-        <v>251</v>
+        <v>287</v>
       </c>
       <c r="C106" t="s">
-        <v>205</v>
+        <v>284</v>
       </c>
       <c r="D106">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="E106" t="s">
         <v>26</v>
@@ -9048,36 +9053,36 @@
         <v>73</v>
       </c>
       <c r="G106" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H106" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I106" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J106" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K106" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="L106" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="B107" t="s">
-        <v>252</v>
+        <v>290</v>
       </c>
       <c r="C107" t="s">
-        <v>205</v>
+        <v>291</v>
       </c>
       <c r="D107">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="E107" t="s">
         <v>26</v>
@@ -9109,13 +9114,13 @@
         <v>199</v>
       </c>
       <c r="B108" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="C108" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D108">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="E108" t="s">
         <v>26</v>
@@ -9124,22 +9129,22 @@
         <v>73</v>
       </c>
       <c r="G108" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="H108" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I108" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J108" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K108" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="L108" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
@@ -9147,10 +9152,10 @@
         <v>199</v>
       </c>
       <c r="B109" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="C109" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D109">
         <v>2015</v>
@@ -9162,22 +9167,22 @@
         <v>73</v>
       </c>
       <c r="G109" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="H109" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I109" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J109" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K109" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="L109" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
@@ -9185,13 +9190,13 @@
         <v>199</v>
       </c>
       <c r="B110" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="C110" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D110">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E110" t="s">
         <v>26</v>
@@ -9223,13 +9228,13 @@
         <v>199</v>
       </c>
       <c r="B111" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="C111" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D111">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="E111" t="s">
         <v>26</v>
@@ -9238,10 +9243,10 @@
         <v>73</v>
       </c>
       <c r="G111" t="s">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="H111" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I111" t="s">
         <v>29</v>
@@ -9253,7 +9258,7 @@
         <v>126</v>
       </c>
       <c r="L111" t="s">
-        <v>126</v>
+        <v>262</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
@@ -9261,13 +9266,13 @@
         <v>199</v>
       </c>
       <c r="B112" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="C112" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D112">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="E112" t="s">
         <v>26</v>
@@ -9276,10 +9281,10 @@
         <v>73</v>
       </c>
       <c r="G112" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="H112" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I112" t="s">
         <v>29</v>
@@ -9288,10 +9293,10 @@
         <v>90</v>
       </c>
       <c r="K112" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="L112" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
@@ -9299,13 +9304,13 @@
         <v>199</v>
       </c>
       <c r="B113" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C113" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D113">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="E113" t="s">
         <v>26</v>
@@ -9334,16 +9339,16 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="8" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="B114" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C114" t="s">
-        <v>203</v>
+        <v>277</v>
       </c>
       <c r="D114">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="E114" t="s">
         <v>26</v>
@@ -9352,7 +9357,7 @@
         <v>73</v>
       </c>
       <c r="G114" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="H114" t="s">
         <v>90</v>
@@ -9361,27 +9366,27 @@
         <v>29</v>
       </c>
       <c r="J114" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K114" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="L114" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="B115" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="C115" t="s">
-        <v>204</v>
+        <v>284</v>
       </c>
       <c r="D115">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="E115" t="s">
         <v>26</v>
@@ -9402,24 +9407,24 @@
         <v>90</v>
       </c>
       <c r="K115" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="L115" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="B116" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="C116" t="s">
-        <v>205</v>
+        <v>291</v>
       </c>
       <c r="D116">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="E116" t="s">
         <v>26</v>
@@ -9448,16 +9453,16 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="B117" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="C117" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="D117">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="E117" t="s">
         <v>26</v>
@@ -9466,36 +9471,36 @@
         <v>73</v>
       </c>
       <c r="G117" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="H117" t="s">
         <v>90</v>
       </c>
       <c r="I117" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J117" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K117" t="s">
         <v>47</v>
       </c>
       <c r="L117" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="B118" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="C118" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="D118">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="E118" t="s">
         <v>26</v>
@@ -9504,19 +9509,19 @@
         <v>73</v>
       </c>
       <c r="G118" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H118" t="s">
         <v>90</v>
       </c>
       <c r="I118" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J118" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K118" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="L118" t="s">
         <v>47</v>
@@ -9524,16 +9529,16 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="B119" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="C119" t="s">
-        <v>277</v>
+        <v>200</v>
       </c>
       <c r="D119">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="E119" t="s">
         <v>26</v>
@@ -9542,36 +9547,36 @@
         <v>73</v>
       </c>
       <c r="G119" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H119" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I119" t="s">
         <v>29</v>
       </c>
       <c r="J119" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K119" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L119" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="B120" t="s">
-        <v>280</v>
+        <v>232</v>
       </c>
       <c r="C120" t="s">
-        <v>277</v>
+        <v>201</v>
       </c>
       <c r="D120">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="E120" t="s">
         <v>26</v>
@@ -9580,36 +9585,36 @@
         <v>73</v>
       </c>
       <c r="G120" t="s">
-        <v>263</v>
+        <v>197</v>
       </c>
       <c r="H120" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I120" t="s">
         <v>29</v>
       </c>
       <c r="J120" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K120" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="L120" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="B121" t="s">
-        <v>281</v>
+        <v>238</v>
       </c>
       <c r="C121" t="s">
-        <v>277</v>
+        <v>202</v>
       </c>
       <c r="D121">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="E121" t="s">
         <v>26</v>
@@ -9618,33 +9623,33 @@
         <v>73</v>
       </c>
       <c r="G121" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H121" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I121" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J121" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="K121" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="L121" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="B122" t="s">
-        <v>282</v>
+        <v>244</v>
       </c>
       <c r="C122" t="s">
-        <v>277</v>
+        <v>203</v>
       </c>
       <c r="D122">
         <v>2016</v>
@@ -9656,7 +9661,7 @@
         <v>73</v>
       </c>
       <c r="G122" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="H122" t="s">
         <v>90</v>
@@ -9665,27 +9670,27 @@
         <v>29</v>
       </c>
       <c r="J122" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K122" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L122" t="s">
-        <v>47</v>
+        <v>262</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="B123" t="s">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="C123" t="s">
-        <v>284</v>
+        <v>204</v>
       </c>
       <c r="D123">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="E123" t="s">
         <v>26</v>
@@ -9706,24 +9711,24 @@
         <v>90</v>
       </c>
       <c r="K123" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L123" t="s">
-        <v>115</v>
+        <v>262</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="B124" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="C124" t="s">
-        <v>284</v>
+        <v>205</v>
       </c>
       <c r="D124">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="E124" t="s">
         <v>26</v>
@@ -9732,22 +9737,22 @@
         <v>73</v>
       </c>
       <c r="G124" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H124" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I124" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J124" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K124" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="L124" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
@@ -9755,13 +9760,13 @@
         <v>264</v>
       </c>
       <c r="B125" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C125" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="D125">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="E125" t="s">
         <v>26</v>
@@ -9770,7 +9775,7 @@
         <v>73</v>
       </c>
       <c r="G125" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H125" t="s">
         <v>90</v>
@@ -9779,13 +9784,13 @@
         <v>29</v>
       </c>
       <c r="J125" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K125" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L125" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
@@ -9793,13 +9798,13 @@
         <v>264</v>
       </c>
       <c r="B126" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C126" t="s">
         <v>284</v>
       </c>
       <c r="D126">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="E126" t="s">
         <v>26</v>
@@ -9808,7 +9813,7 @@
         <v>73</v>
       </c>
       <c r="G126" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H126" t="s">
         <v>90</v>
@@ -9820,10 +9825,10 @@
         <v>90</v>
       </c>
       <c r="K126" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L126" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
@@ -9831,13 +9836,13 @@
         <v>264</v>
       </c>
       <c r="B127" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C127" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="D127">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="E127" t="s">
         <v>26</v>
@@ -9846,33 +9851,33 @@
         <v>73</v>
       </c>
       <c r="G127" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H127" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I127" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J127" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K127" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="L127" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="B128" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="C128" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="D128">
         <v>2016</v>
@@ -9884,13 +9889,13 @@
         <v>73</v>
       </c>
       <c r="G128" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="H128" t="s">
         <v>90</v>
       </c>
       <c r="I128" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J128" t="s">
         <v>90</v>
@@ -9904,16 +9909,16 @@
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="B129" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="C129" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D129">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="E129" t="s">
         <v>26</v>
@@ -9922,36 +9927,36 @@
         <v>73</v>
       </c>
       <c r="G129" t="s">
-        <v>73</v>
+        <v>263</v>
       </c>
       <c r="H129" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I129" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="J129" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K129" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="L129" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="B130" t="s">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="C130" t="s">
-        <v>291</v>
+        <v>200</v>
       </c>
       <c r="D130">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="E130" t="s">
         <v>26</v>
@@ -9960,36 +9965,36 @@
         <v>73</v>
       </c>
       <c r="G130" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="H130" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I130" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J130" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K130" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="L130" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="B131" t="s">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="C131" t="s">
-        <v>291</v>
+        <v>201</v>
       </c>
       <c r="D131">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E131" t="s">
         <v>26</v>
@@ -9998,33 +10003,33 @@
         <v>73</v>
       </c>
       <c r="G131" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="H131" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I131" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J131" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K131" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="L131" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="B132" t="s">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="C132" t="s">
-        <v>277</v>
+        <v>202</v>
       </c>
       <c r="D132">
         <v>2017</v>
@@ -10036,33 +10041,33 @@
         <v>73</v>
       </c>
       <c r="G132" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H132" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I132" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J132" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="K132" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="L132" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="B133" t="s">
-        <v>295</v>
+        <v>259</v>
       </c>
       <c r="C133" t="s">
-        <v>284</v>
+        <v>203</v>
       </c>
       <c r="D133">
         <v>2017</v>
@@ -10074,7 +10079,7 @@
         <v>73</v>
       </c>
       <c r="G133" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="H133" t="s">
         <v>90</v>
@@ -10086,21 +10091,21 @@
         <v>90</v>
       </c>
       <c r="K133" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L133" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
-        <v>264</v>
+        <v>199</v>
       </c>
       <c r="B134" t="s">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="C134" t="s">
-        <v>291</v>
+        <v>204</v>
       </c>
       <c r="D134">
         <v>2017</v>
@@ -10112,36 +10117,36 @@
         <v>73</v>
       </c>
       <c r="G134" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H134" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I134" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J134" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K134" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="L134" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
-        <v>318</v>
+        <v>199</v>
       </c>
       <c r="B135" t="s">
-        <v>304</v>
+        <v>261</v>
       </c>
       <c r="C135" t="s">
-        <v>298</v>
+        <v>205</v>
       </c>
       <c r="D135">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="E135" t="s">
         <v>26</v>
@@ -10150,36 +10155,36 @@
         <v>73</v>
       </c>
       <c r="G135" t="s">
-        <v>263</v>
+        <v>73</v>
       </c>
       <c r="H135" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I135" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="J135" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K135" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="L135" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="B136" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="C136" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="D136">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="E136" t="s">
         <v>26</v>
@@ -10188,16 +10193,16 @@
         <v>73</v>
       </c>
       <c r="G136" t="s">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="H136" t="s">
         <v>90</v>
       </c>
       <c r="I136" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J136" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K136" t="s">
         <v>47</v>
@@ -10208,13 +10213,13 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="B137" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C137" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="D137">
         <v>2017</v>
@@ -10226,19 +10231,19 @@
         <v>73</v>
       </c>
       <c r="G137" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H137" t="s">
         <v>90</v>
       </c>
       <c r="I137" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J137" t="s">
         <v>90</v>
       </c>
       <c r="K137" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="L137" t="s">
         <v>47</v>
@@ -10246,16 +10251,16 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="B138" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="C138" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D138">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="E138" t="s">
         <v>26</v>
@@ -10264,22 +10269,22 @@
         <v>73</v>
       </c>
       <c r="G138" t="s">
-        <v>263</v>
+        <v>73</v>
       </c>
       <c r="H138" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I138" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="J138" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K138" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="L138" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
@@ -10287,13 +10292,13 @@
         <v>318</v>
       </c>
       <c r="B139" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C139" t="s">
         <v>298</v>
       </c>
       <c r="D139">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="E139" t="s">
         <v>26</v>
@@ -10302,7 +10307,7 @@
         <v>73</v>
       </c>
       <c r="G139" t="s">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="H139" t="s">
         <v>90</v>
@@ -10314,7 +10319,7 @@
         <v>90</v>
       </c>
       <c r="K139" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="L139" t="s">
         <v>47</v>
@@ -10325,13 +10330,13 @@
         <v>318</v>
       </c>
       <c r="B140" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C140" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D140">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="E140" t="s">
         <v>26</v>
@@ -10360,16 +10365,16 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B141" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="C141" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="D141">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="E141" t="s">
         <v>26</v>
@@ -10378,36 +10383,36 @@
         <v>73</v>
       </c>
       <c r="G141" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="H141" t="s">
         <v>90</v>
       </c>
       <c r="I141" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J141" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K141" t="s">
+        <v>45</v>
+      </c>
+      <c r="L141" t="s">
         <v>47</v>
-      </c>
-      <c r="L141" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B142" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="C142" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="D142">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="E142" t="s">
         <v>26</v>
@@ -10416,22 +10421,22 @@
         <v>73</v>
       </c>
       <c r="G142" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H142" t="s">
         <v>90</v>
       </c>
       <c r="I142" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J142" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K142" t="s">
-        <v>115</v>
+        <v>339</v>
       </c>
       <c r="L142" t="s">
-        <v>47</v>
+        <v>338</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
@@ -10439,13 +10444,13 @@
         <v>318</v>
       </c>
       <c r="B143" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C143" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D143">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="E143" t="s">
         <v>26</v>
@@ -10477,13 +10482,13 @@
         <v>318</v>
       </c>
       <c r="B144" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C144" t="s">
         <v>299</v>
       </c>
       <c r="D144">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E144" t="s">
         <v>26</v>
@@ -10492,7 +10497,7 @@
         <v>73</v>
       </c>
       <c r="G144" t="s">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="H144" t="s">
         <v>90</v>
@@ -10504,21 +10509,21 @@
         <v>90</v>
       </c>
       <c r="K144" t="s">
+        <v>47</v>
+      </c>
+      <c r="L144" t="s">
         <v>115</v>
-      </c>
-      <c r="L144" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B145" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="C145" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="D145">
         <v>2018</v>
@@ -10530,36 +10535,36 @@
         <v>73</v>
       </c>
       <c r="G145" t="s">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="H145" t="s">
         <v>90</v>
       </c>
       <c r="I145" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J145" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K145" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L145" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B146" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="C146" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="D146">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E146" t="s">
         <v>26</v>
@@ -10568,39 +10573,39 @@
         <v>73</v>
       </c>
       <c r="G146" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="H146" t="s">
         <v>90</v>
       </c>
       <c r="I146" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J146" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K146" t="s">
         <v>47</v>
       </c>
       <c r="L146" t="s">
-        <v>47</v>
+        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="8" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="B147" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="C147" t="s">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c r="D147">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="E147" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F147" t="s">
         <v>73</v>
@@ -10618,39 +10623,39 @@
         <v>90</v>
       </c>
       <c r="K147" t="s">
-        <v>115</v>
+        <v>361</v>
       </c>
       <c r="L147" t="s">
-        <v>47</v>
+        <v>363</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="8" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="B148" t="s">
-        <v>317</v>
+        <v>353</v>
       </c>
       <c r="C148" t="s">
-        <v>299</v>
+        <v>340</v>
       </c>
       <c r="D148">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="E148" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F148" t="s">
         <v>73</v>
       </c>
       <c r="G148" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="H148" t="s">
         <v>90</v>
       </c>
       <c r="I148" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J148" t="s">
         <v>90</v>
@@ -10664,89 +10669,89 @@
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="B149" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="C149" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="D149">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E149" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F149" t="s">
         <v>73</v>
       </c>
       <c r="G149" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="H149" t="s">
         <v>90</v>
       </c>
       <c r="I149" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J149" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K149" t="s">
         <v>45</v>
       </c>
       <c r="L149" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A150" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="B150" t="s">
+        <v>308</v>
+      </c>
+      <c r="C150" t="s">
+        <v>298</v>
+      </c>
+      <c r="D150">
+        <v>2019</v>
+      </c>
+      <c r="E150" t="s">
+        <v>26</v>
+      </c>
+      <c r="F150" t="s">
+        <v>73</v>
+      </c>
+      <c r="G150" t="s">
+        <v>263</v>
+      </c>
+      <c r="H150" t="s">
+        <v>90</v>
+      </c>
+      <c r="I150" t="s">
+        <v>90</v>
+      </c>
+      <c r="J150" t="s">
+        <v>90</v>
+      </c>
+      <c r="K150" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>319</v>
-      </c>
-      <c r="B150" t="s">
-        <v>328</v>
-      </c>
-      <c r="C150" t="s">
-        <v>320</v>
-      </c>
-      <c r="D150">
-        <v>2018</v>
-      </c>
-      <c r="E150" t="s">
-        <v>26</v>
-      </c>
-      <c r="F150" t="s">
-        <v>73</v>
-      </c>
-      <c r="G150" t="s">
-        <v>79</v>
-      </c>
-      <c r="H150" t="s">
-        <v>90</v>
-      </c>
-      <c r="I150" t="s">
-        <v>29</v>
-      </c>
-      <c r="J150" t="s">
-        <v>29</v>
-      </c>
-      <c r="K150" t="s">
-        <v>45</v>
-      </c>
       <c r="L150" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>319</v>
+      <c r="A151" s="18" t="s">
+        <v>318</v>
       </c>
       <c r="B151" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="C151" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="D151">
         <v>2019</v>
@@ -10758,22 +10763,22 @@
         <v>73</v>
       </c>
       <c r="G151" t="s">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="H151" t="s">
         <v>90</v>
       </c>
       <c r="I151" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J151" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K151" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L151" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
@@ -10781,13 +10786,13 @@
         <v>319</v>
       </c>
       <c r="B152" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C152" t="s">
         <v>320</v>
       </c>
       <c r="D152">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E152" t="s">
         <v>26</v>
@@ -10819,13 +10824,13 @@
         <v>319</v>
       </c>
       <c r="B153" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C153" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D153">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="E153" t="s">
         <v>26</v>
@@ -10849,24 +10854,24 @@
         <v>47</v>
       </c>
       <c r="L153" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="B154" t="s">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="C154" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="D154">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="E154" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F154" t="s">
         <v>73</v>
@@ -10881,30 +10886,30 @@
         <v>29</v>
       </c>
       <c r="J154" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K154" t="s">
-        <v>339</v>
+        <v>81</v>
       </c>
       <c r="L154" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="B155" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="C155" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="D155">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E155" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F155" t="s">
         <v>73</v>
@@ -10916,39 +10921,39 @@
         <v>90</v>
       </c>
       <c r="I155" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J155" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K155" t="s">
+        <v>115</v>
+      </c>
+      <c r="L155" t="s">
         <v>47</v>
-      </c>
-      <c r="L155" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="B156" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="C156" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="D156">
         <v>2019</v>
       </c>
       <c r="E156" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F156" t="s">
         <v>73</v>
       </c>
       <c r="G156" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H156" t="s">
         <v>90</v>
@@ -10957,27 +10962,27 @@
         <v>29</v>
       </c>
       <c r="J156" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K156" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L156" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="B157" t="s">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="C157" t="s">
-        <v>321</v>
+        <v>365</v>
       </c>
       <c r="D157">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E157" t="s">
         <v>26</v>
@@ -10995,10 +11000,10 @@
         <v>29</v>
       </c>
       <c r="J157" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K157" t="s">
-        <v>47</v>
+        <v>382</v>
       </c>
       <c r="L157" t="s">
         <v>47</v>
@@ -11006,16 +11011,16 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="B158" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="C158" t="s">
-        <v>321</v>
+        <v>366</v>
       </c>
       <c r="D158">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="E158" t="s">
         <v>26</v>
@@ -11030,10 +11035,10 @@
         <v>90</v>
       </c>
       <c r="I158" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J158" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K158" t="s">
         <v>47</v>
@@ -11044,28 +11049,28 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>344</v>
+        <v>414</v>
       </c>
       <c r="B159" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="C159" t="s">
-        <v>341</v>
+        <v>384</v>
       </c>
       <c r="D159">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E159" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F159" t="s">
         <v>73</v>
       </c>
       <c r="G159" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H159" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I159" t="s">
         <v>90</v>
@@ -11074,36 +11079,36 @@
         <v>90</v>
       </c>
       <c r="K159" t="s">
-        <v>361</v>
+        <v>81</v>
       </c>
       <c r="L159" t="s">
-        <v>363</v>
+        <v>81</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>344</v>
+        <v>415</v>
       </c>
       <c r="B160" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C160" t="s">
-        <v>341</v>
+        <v>385</v>
       </c>
       <c r="D160">
         <v>2019</v>
       </c>
       <c r="E160" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F160" t="s">
         <v>73</v>
       </c>
       <c r="G160" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H160" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I160" t="s">
         <v>29</v>
@@ -11115,24 +11120,24 @@
         <v>81</v>
       </c>
       <c r="L160" t="s">
-        <v>361</v>
+        <v>81</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>344</v>
+        <v>413</v>
       </c>
       <c r="B161" t="s">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="C161" t="s">
-        <v>341</v>
+        <v>400</v>
       </c>
       <c r="D161">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E161" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F161" t="s">
         <v>73</v>
@@ -11147,74 +11152,74 @@
         <v>90</v>
       </c>
       <c r="J161" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K161" t="s">
-        <v>362</v>
+        <v>408</v>
       </c>
       <c r="L161" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>344</v>
+        <v>416</v>
       </c>
       <c r="B162" t="s">
-        <v>353</v>
+        <v>424</v>
       </c>
       <c r="C162" t="s">
-        <v>340</v>
+        <v>401</v>
       </c>
       <c r="D162">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E162" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F162" t="s">
         <v>73</v>
       </c>
       <c r="G162" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="H162" t="s">
         <v>90</v>
       </c>
       <c r="I162" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J162" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K162" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L162" t="s">
-        <v>115</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
-        <v>344</v>
+      <c r="A163" s="18" t="s">
+        <v>318</v>
       </c>
       <c r="B163" t="s">
-        <v>354</v>
+        <v>309</v>
       </c>
       <c r="C163" t="s">
-        <v>340</v>
+        <v>298</v>
       </c>
       <c r="D163">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E163" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F163" t="s">
         <v>73</v>
       </c>
       <c r="G163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H163" t="s">
         <v>90</v>
@@ -11233,102 +11238,102 @@
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>344</v>
+      <c r="A164" s="18" t="s">
+        <v>318</v>
       </c>
       <c r="B164" t="s">
-        <v>355</v>
+        <v>316</v>
       </c>
       <c r="C164" t="s">
-        <v>340</v>
+        <v>299</v>
       </c>
       <c r="D164">
         <v>2020</v>
       </c>
       <c r="E164" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F164" t="s">
         <v>73</v>
       </c>
       <c r="G164" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H164" t="s">
         <v>90</v>
       </c>
       <c r="I164" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J164" t="s">
         <v>90</v>
       </c>
       <c r="K164" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="L164" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="B165" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="C165" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="D165">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="E165" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F165" t="s">
         <v>73</v>
       </c>
       <c r="G165" t="s">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="H165" t="s">
         <v>90</v>
       </c>
       <c r="I165" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J165" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K165" t="s">
         <v>45</v>
       </c>
       <c r="L165" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="B166" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="C166" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="D166">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E166" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F166" t="s">
         <v>73</v>
       </c>
       <c r="G166" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H166" t="s">
         <v>90</v>
@@ -11337,13 +11342,13 @@
         <v>29</v>
       </c>
       <c r="J166" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K166" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L166" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
@@ -11351,10 +11356,10 @@
         <v>344</v>
       </c>
       <c r="B167" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C167" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D167">
         <v>2020</v>
@@ -11366,39 +11371,39 @@
         <v>73</v>
       </c>
       <c r="G167" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H167" t="s">
         <v>90</v>
       </c>
       <c r="I167" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J167" t="s">
         <v>90</v>
       </c>
       <c r="K167" t="s">
-        <v>45</v>
+        <v>362</v>
       </c>
       <c r="L167" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="B168" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="C168" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
       <c r="D168">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E168" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F168" t="s">
         <v>73</v>
@@ -11416,39 +11421,39 @@
         <v>90</v>
       </c>
       <c r="K168" t="s">
-        <v>382</v>
+        <v>81</v>
       </c>
       <c r="L168" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="B169" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="C169" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="D169">
         <v>2020</v>
       </c>
       <c r="E169" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F169" t="s">
         <v>73</v>
       </c>
       <c r="G169" t="s">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="H169" t="s">
         <v>90</v>
       </c>
       <c r="I169" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J169" t="s">
         <v>90</v>
@@ -11457,7 +11462,7 @@
         <v>45</v>
       </c>
       <c r="L169" t="s">
-        <v>382</v>
+        <v>45</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
@@ -11465,13 +11470,13 @@
         <v>364</v>
       </c>
       <c r="B170" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C170" t="s">
         <v>365</v>
       </c>
       <c r="D170">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E170" t="s">
         <v>26</v>
@@ -11480,7 +11485,7 @@
         <v>73</v>
       </c>
       <c r="G170" t="s">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="H170" t="s">
         <v>90</v>
@@ -11495,7 +11500,7 @@
         <v>45</v>
       </c>
       <c r="L170" t="s">
-        <v>45</v>
+        <v>382</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
@@ -11503,13 +11508,13 @@
         <v>364</v>
       </c>
       <c r="B171" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C171" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D171">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="E171" t="s">
         <v>26</v>
@@ -11518,7 +11523,7 @@
         <v>73</v>
       </c>
       <c r="G171" t="s">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="H171" t="s">
         <v>90</v>
@@ -11530,24 +11535,24 @@
         <v>90</v>
       </c>
       <c r="K171" t="s">
-        <v>45</v>
+        <v>383</v>
       </c>
       <c r="L171" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>364</v>
+        <v>414</v>
       </c>
       <c r="B172" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="C172" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="D172">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="E172" t="s">
         <v>26</v>
@@ -11556,10 +11561,10 @@
         <v>73</v>
       </c>
       <c r="G172" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H172" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I172" t="s">
         <v>90</v>
@@ -11568,24 +11573,24 @@
         <v>90</v>
       </c>
       <c r="K172" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="L172" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>364</v>
+        <v>415</v>
       </c>
       <c r="B173" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="C173" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="D173">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E173" t="s">
         <v>26</v>
@@ -11597,30 +11602,30 @@
         <v>80</v>
       </c>
       <c r="H173" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I173" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J173" t="s">
         <v>90</v>
       </c>
       <c r="K173" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="L173" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>364</v>
+        <v>413</v>
       </c>
       <c r="B174" t="s">
-        <v>373</v>
+        <v>419</v>
       </c>
       <c r="C174" t="s">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="D174">
         <v>2020</v>
@@ -11641,27 +11646,27 @@
         <v>90</v>
       </c>
       <c r="J174" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K174" t="s">
-        <v>383</v>
+        <v>423</v>
       </c>
       <c r="L174" t="s">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>364</v>
+        <v>416</v>
       </c>
       <c r="B175" t="s">
-        <v>374</v>
+        <v>425</v>
       </c>
       <c r="C175" t="s">
-        <v>366</v>
+        <v>401</v>
       </c>
       <c r="D175">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E175" t="s">
         <v>26</v>
@@ -11679,27 +11684,27 @@
         <v>90</v>
       </c>
       <c r="J175" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K175" t="s">
-        <v>383</v>
+        <v>45</v>
       </c>
       <c r="L175" t="s">
-        <v>383</v>
+        <v>45</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
-        <v>364</v>
+      <c r="A176" s="18" t="s">
+        <v>318</v>
       </c>
       <c r="B176" t="s">
-        <v>375</v>
+        <v>310</v>
       </c>
       <c r="C176" t="s">
-        <v>366</v>
+        <v>298</v>
       </c>
       <c r="D176">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E176" t="s">
         <v>26</v>
@@ -11708,7 +11713,7 @@
         <v>73</v>
       </c>
       <c r="G176" t="s">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="H176" t="s">
         <v>90</v>
@@ -11720,24 +11725,24 @@
         <v>90</v>
       </c>
       <c r="K176" t="s">
+        <v>47</v>
+      </c>
+      <c r="L176" t="s">
         <v>115</v>
       </c>
-      <c r="L176" t="s">
-        <v>383</v>
-      </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
-        <v>364</v>
+      <c r="A177" s="18" t="s">
+        <v>318</v>
       </c>
       <c r="B177" t="s">
-        <v>376</v>
+        <v>317</v>
       </c>
       <c r="C177" t="s">
-        <v>366</v>
+        <v>299</v>
       </c>
       <c r="D177">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E177" t="s">
         <v>26</v>
@@ -11746,7 +11751,7 @@
         <v>73</v>
       </c>
       <c r="G177" t="s">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="H177" t="s">
         <v>90</v>
@@ -11766,16 +11771,16 @@
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>414</v>
+        <v>319</v>
       </c>
       <c r="B178" t="s">
-        <v>390</v>
+        <v>331</v>
       </c>
       <c r="C178" t="s">
-        <v>384</v>
+        <v>320</v>
       </c>
       <c r="D178">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="E178" t="s">
         <v>26</v>
@@ -11784,36 +11789,36 @@
         <v>73</v>
       </c>
       <c r="G178" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H178" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I178" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J178" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K178" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L178" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>414</v>
+        <v>319</v>
       </c>
       <c r="B179" t="s">
-        <v>391</v>
+        <v>336</v>
       </c>
       <c r="C179" t="s">
-        <v>384</v>
+        <v>321</v>
       </c>
       <c r="D179">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E179" t="s">
         <v>26</v>
@@ -11822,33 +11827,33 @@
         <v>73</v>
       </c>
       <c r="G179" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H179" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I179" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J179" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K179" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L179" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>414</v>
+        <v>364</v>
       </c>
       <c r="B180" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="C180" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="D180">
         <v>2021</v>
@@ -11860,36 +11865,36 @@
         <v>73</v>
       </c>
       <c r="G180" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="H180" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I180" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J180" t="s">
         <v>90</v>
       </c>
       <c r="K180" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="L180" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>414</v>
+        <v>364</v>
       </c>
       <c r="B181" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="C181" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="D181">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E181" t="s">
         <v>26</v>
@@ -11898,22 +11903,22 @@
         <v>73</v>
       </c>
       <c r="G181" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="H181" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I181" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J181" t="s">
         <v>90</v>
       </c>
       <c r="K181" t="s">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="L181" t="s">
-        <v>81</v>
+        <v>383</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
@@ -11921,13 +11926,13 @@
         <v>414</v>
       </c>
       <c r="B182" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C182" t="s">
         <v>384</v>
       </c>
       <c r="D182">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E182" t="s">
         <v>26</v>
@@ -11959,13 +11964,13 @@
         <v>415</v>
       </c>
       <c r="B183" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C183" t="s">
         <v>385</v>
       </c>
       <c r="D183">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="E183" t="s">
         <v>26</v>
@@ -11989,21 +11994,21 @@
         <v>81</v>
       </c>
       <c r="L183" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B184" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="C184" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="D184">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E184" t="s">
         <v>26</v>
@@ -12012,33 +12017,33 @@
         <v>73</v>
       </c>
       <c r="G184" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H184" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I184" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J184" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K184" t="s">
-        <v>115</v>
+        <v>423</v>
       </c>
       <c r="L184" t="s">
-        <v>81</v>
+        <v>423</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B185" t="s">
-        <v>394</v>
+        <v>426</v>
       </c>
       <c r="C185" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="D185">
         <v>2021</v>
@@ -12050,36 +12055,36 @@
         <v>73</v>
       </c>
       <c r="G185" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H185" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I185" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J185" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K185" t="s">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="L185" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B186" t="s">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="C186" t="s">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="D186">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E186" t="s">
         <v>26</v>
@@ -12088,36 +12093,36 @@
         <v>73</v>
       </c>
       <c r="G186" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H186" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I186" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J186" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K186" t="s">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="L186" t="s">
-        <v>81</v>
+        <v>433</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>415</v>
+        <v>364</v>
       </c>
       <c r="B187" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="C187" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="D187">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E187" t="s">
         <v>26</v>
@@ -12129,33 +12134,33 @@
         <v>79</v>
       </c>
       <c r="H187" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I187" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J187" t="s">
         <v>90</v>
       </c>
       <c r="K187" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="L187" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>413</v>
+        <v>364</v>
       </c>
       <c r="B188" t="s">
-        <v>418</v>
+        <v>375</v>
       </c>
       <c r="C188" t="s">
-        <v>400</v>
+        <v>366</v>
       </c>
       <c r="D188">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="E188" t="s">
         <v>26</v>
@@ -12164,7 +12169,7 @@
         <v>73</v>
       </c>
       <c r="G188" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H188" t="s">
         <v>90</v>
@@ -12173,27 +12178,27 @@
         <v>90</v>
       </c>
       <c r="J188" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K188" t="s">
-        <v>408</v>
+        <v>115</v>
       </c>
       <c r="L188" t="s">
-        <v>45</v>
+        <v>383</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B189" t="s">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="C189" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="D189">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="E189" t="s">
         <v>26</v>
@@ -12202,36 +12207,36 @@
         <v>73</v>
       </c>
       <c r="G189" t="s">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="H189" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I189" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J189" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K189" t="s">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="L189" t="s">
-        <v>408</v>
+        <v>81</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B190" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="C190" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="D190">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E190" t="s">
         <v>26</v>
@@ -12243,19 +12248,19 @@
         <v>79</v>
       </c>
       <c r="H190" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I190" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J190" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K190" t="s">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="L190" t="s">
-        <v>423</v>
+        <v>81</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
@@ -12298,16 +12303,16 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B192" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C192" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D192">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E192" t="s">
         <v>26</v>
@@ -12328,24 +12333,24 @@
         <v>29</v>
       </c>
       <c r="K192" t="s">
+        <v>429</v>
+      </c>
+      <c r="L192" t="s">
         <v>408</v>
-      </c>
-      <c r="L192" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B193" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C193" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D193">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="E193" t="s">
         <v>26</v>
@@ -12354,7 +12359,7 @@
         <v>73</v>
       </c>
       <c r="G193" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="H193" t="s">
         <v>90</v>
@@ -12363,27 +12368,27 @@
         <v>90</v>
       </c>
       <c r="J193" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K193" t="s">
-        <v>45</v>
+        <v>429</v>
       </c>
       <c r="L193" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="B194" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="C194" t="s">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="D194">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="E194" t="s">
         <v>26</v>
@@ -12398,30 +12403,30 @@
         <v>90</v>
       </c>
       <c r="I194" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J194" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K194" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="L194" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
       <c r="B195" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="C195" t="s">
-        <v>401</v>
+        <v>438</v>
       </c>
       <c r="D195">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E195" t="s">
         <v>26</v>
@@ -12430,36 +12435,36 @@
         <v>73</v>
       </c>
       <c r="G195" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H195" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I195" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J195" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K195" t="s">
-        <v>408</v>
+        <v>197</v>
       </c>
       <c r="L195" t="s">
-        <v>45</v>
+        <v>197</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>416</v>
+        <v>364</v>
       </c>
       <c r="B196" t="s">
-        <v>427</v>
+        <v>380</v>
       </c>
       <c r="C196" t="s">
-        <v>401</v>
+        <v>365</v>
       </c>
       <c r="D196">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E196" t="s">
         <v>26</v>
@@ -12468,7 +12473,7 @@
         <v>73</v>
       </c>
       <c r="G196" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H196" t="s">
         <v>90</v>
@@ -12477,24 +12482,24 @@
         <v>90</v>
       </c>
       <c r="J196" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K196" t="s">
-        <v>429</v>
+        <v>45</v>
       </c>
       <c r="L196" t="s">
-        <v>408</v>
+        <v>45</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>416</v>
+        <v>364</v>
       </c>
       <c r="B197" t="s">
-        <v>428</v>
+        <v>376</v>
       </c>
       <c r="C197" t="s">
-        <v>401</v>
+        <v>366</v>
       </c>
       <c r="D197">
         <v>2023</v>
@@ -12515,27 +12520,27 @@
         <v>90</v>
       </c>
       <c r="J197" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K197" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L197" t="s">
-        <v>429</v>
+        <v>115</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B198" t="s">
-        <v>430</v>
+        <v>399</v>
       </c>
       <c r="C198" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="D198">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E198" t="s">
         <v>26</v>
@@ -12544,36 +12549,36 @@
         <v>73</v>
       </c>
       <c r="G198" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H198" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I198" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J198" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K198" t="s">
-        <v>408</v>
+        <v>81</v>
       </c>
       <c r="L198" t="s">
-        <v>433</v>
+        <v>81</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B199" t="s">
-        <v>431</v>
+        <v>396</v>
       </c>
       <c r="C199" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="D199">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E199" t="s">
         <v>26</v>
@@ -12582,33 +12587,33 @@
         <v>73</v>
       </c>
       <c r="G199" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H199" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I199" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J199" t="s">
         <v>90</v>
       </c>
       <c r="K199" t="s">
-        <v>429</v>
+        <v>81</v>
       </c>
       <c r="L199" t="s">
-        <v>408</v>
+        <v>81</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B200" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C200" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D200">
         <v>2023</v>
@@ -12632,24 +12637,24 @@
         <v>29</v>
       </c>
       <c r="K200" t="s">
-        <v>45</v>
+        <v>408</v>
       </c>
       <c r="L200" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="B201" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="C201" t="s">
-        <v>437</v>
+        <v>401</v>
       </c>
       <c r="D201">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E201" t="s">
         <v>26</v>
@@ -12664,27 +12669,27 @@
         <v>90</v>
       </c>
       <c r="I201" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J201" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K201" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="L201" t="s">
-        <v>81</v>
+        <v>429</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="B202" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="C202" t="s">
-        <v>437</v>
+        <v>402</v>
       </c>
       <c r="D202">
         <v>2023</v>
@@ -12696,36 +12701,36 @@
         <v>73</v>
       </c>
       <c r="G202" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="H202" t="s">
         <v>90</v>
       </c>
       <c r="I202" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J202" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K202" t="s">
         <v>45</v>
       </c>
       <c r="L202" t="s">
-        <v>81</v>
+        <v>429</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B203" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C203" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D203">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E203" t="s">
         <v>26</v>
@@ -12734,10 +12739,10 @@
         <v>73</v>
       </c>
       <c r="G203" t="s">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="H203" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I203" t="s">
         <v>29</v>
@@ -12746,13 +12751,16 @@
         <v>90</v>
       </c>
       <c r="K203" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="L203" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L203">
+    <sortCondition ref="D1:D203"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/00_Data/DF EOF Site & Year Metadata (2004-2023).xlsx
+++ b/00_Data/DF EOF Site & Year Metadata (2004-2023).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwprod-my.sharepoint.com/personal/zchen2545_wisc_edu/Documents/Research/Discovery Farms/DF Runoff Generation/Github repo/DF_runoff/00_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{B78423C8-A332-48E0-B5C7-5F938FB9312B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2B78396-9E5D-44A0-9E80-6EDE0BBE8160}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{B78423C8-A332-48E0-B5C7-5F938FB9312B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D0819EF-34BA-4ED8-9C0B-4E4F8412BF9F}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="1272" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site" sheetId="1" r:id="rId1"/>
@@ -5083,37 +5083,37 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>413</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>418</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>400</v>
       </c>
       <c r="D2">
-        <v>2004</v>
+        <v>2019</v>
       </c>
       <c r="E2" t="s">
         <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s">
         <v>90</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J2" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>45</v>
+        <v>408</v>
       </c>
       <c r="L2" t="s">
         <v>45</v>
@@ -5121,16 +5121,16 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>413</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>419</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>400</v>
       </c>
       <c r="D3">
-        <v>2004</v>
+        <v>2020</v>
       </c>
       <c r="E3" t="s">
         <v>26</v>
@@ -5139,42 +5139,42 @@
         <v>73</v>
       </c>
       <c r="G3" t="s">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="H3" t="s">
         <v>90</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J3" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K3" t="s">
-        <v>45</v>
+        <v>423</v>
       </c>
       <c r="L3" t="s">
-        <v>45</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>413</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>420</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>400</v>
       </c>
       <c r="D4">
-        <v>2004</v>
+        <v>2021</v>
       </c>
       <c r="E4" t="s">
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s">
         <v>79</v>
@@ -5183,30 +5183,30 @@
         <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J4" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>423</v>
       </c>
       <c r="L4" t="s">
-        <v>45</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>421</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="D5">
-        <v>2004</v>
+        <v>2022</v>
       </c>
       <c r="E5" t="s">
         <v>26</v>
@@ -5215,36 +5215,36 @@
         <v>73</v>
       </c>
       <c r="G5" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J5" t="s">
-        <v>176</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
-        <v>47</v>
+        <v>423</v>
       </c>
       <c r="L5" t="s">
-        <v>47</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>422</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="D6">
-        <v>2004</v>
+        <v>2023</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
@@ -5253,36 +5253,36 @@
         <v>73</v>
       </c>
       <c r="G6" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J6" t="s">
-        <v>176</v>
+        <v>29</v>
       </c>
       <c r="K6" t="s">
-        <v>47</v>
+        <v>408</v>
       </c>
       <c r="L6" t="s">
-        <v>47</v>
+        <v>423</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>424</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>401</v>
       </c>
       <c r="D7">
-        <v>2004</v>
+        <v>2019</v>
       </c>
       <c r="E7" t="s">
         <v>26</v>
@@ -5291,57 +5291,57 @@
         <v>73</v>
       </c>
       <c r="G7" t="s">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I7" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J7" t="s">
-        <v>176</v>
+        <v>29</v>
       </c>
       <c r="K7" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="L7" t="s">
-        <v>47</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>416</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>425</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>401</v>
       </c>
       <c r="D8">
-        <v>2005</v>
+        <v>2020</v>
       </c>
       <c r="E8" t="s">
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s">
         <v>90</v>
       </c>
       <c r="I8" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J8" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K8" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="L8" t="s">
         <v>45</v>
@@ -5349,16 +5349,16 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>416</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>426</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>401</v>
       </c>
       <c r="D9">
-        <v>2005</v>
+        <v>2021</v>
       </c>
       <c r="E9" t="s">
         <v>26</v>
@@ -5373,13 +5373,13 @@
         <v>90</v>
       </c>
       <c r="I9" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J9" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K9" t="s">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="L9" t="s">
         <v>45</v>
@@ -5387,22 +5387,22 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>416</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>427</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>401</v>
       </c>
       <c r="D10">
-        <v>2005</v>
+        <v>2022</v>
       </c>
       <c r="E10" t="s">
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s">
         <v>80</v>
@@ -5411,74 +5411,74 @@
         <v>90</v>
       </c>
       <c r="I10" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J10" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K10" t="s">
-        <v>81</v>
+        <v>429</v>
       </c>
       <c r="L10" t="s">
-        <v>45</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>416</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>428</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>401</v>
       </c>
       <c r="D11">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s">
         <v>90</v>
       </c>
       <c r="I11" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K11" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="L11" t="s">
-        <v>45</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>417</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>430</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>402</v>
       </c>
       <c r="D12">
-        <v>2005</v>
+        <v>2021</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
         <v>80</v>
@@ -5487,30 +5487,30 @@
         <v>90</v>
       </c>
       <c r="I12" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J12" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K12" t="s">
-        <v>81</v>
+        <v>408</v>
       </c>
       <c r="L12" t="s">
-        <v>45</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>431</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="D13">
-        <v>2005</v>
+        <v>2022</v>
       </c>
       <c r="E13" t="s">
         <v>26</v>
@@ -5519,36 +5519,36 @@
         <v>73</v>
       </c>
       <c r="G13" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I13" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J13" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K13" t="s">
-        <v>115</v>
+        <v>429</v>
       </c>
       <c r="L13" t="s">
-        <v>47</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>432</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="D14">
-        <v>2005</v>
+        <v>2023</v>
       </c>
       <c r="E14" t="s">
         <v>26</v>
@@ -5557,74 +5557,74 @@
         <v>73</v>
       </c>
       <c r="G14" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I14" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J14" t="s">
-        <v>176</v>
+        <v>29</v>
       </c>
       <c r="K14" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="L14" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="B15" t="s">
+        <v>327</v>
+      </c>
+      <c r="C15" t="s">
+        <v>320</v>
+      </c>
+      <c r="D15">
+        <v>2017</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" t="s">
+        <v>45</v>
+      </c>
+      <c r="L15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15">
-        <v>2005</v>
-      </c>
-      <c r="E15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" t="s">
-        <v>114</v>
-      </c>
-      <c r="H15" t="s">
-        <v>29</v>
-      </c>
-      <c r="I15" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15" t="s">
-        <v>176</v>
-      </c>
-      <c r="K15" t="s">
-        <v>47</v>
-      </c>
-      <c r="L15" t="s">
-        <v>115</v>
-      </c>
-    </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>117</v>
+      <c r="A16" s="18" t="s">
+        <v>319</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>328</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>320</v>
       </c>
       <c r="D16">
-        <v>2005</v>
+        <v>2018</v>
       </c>
       <c r="E16" t="s">
         <v>26</v>
@@ -5633,7 +5633,7 @@
         <v>73</v>
       </c>
       <c r="G16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s">
         <v>90</v>
@@ -5642,27 +5642,27 @@
         <v>29</v>
       </c>
       <c r="J16" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K16" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="L16" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
-        <v>150</v>
+      <c r="A17" t="s">
+        <v>319</v>
       </c>
       <c r="B17" t="s">
-        <v>177</v>
+        <v>329</v>
       </c>
       <c r="C17" t="s">
-        <v>154</v>
+        <v>320</v>
       </c>
       <c r="D17">
-        <v>2005</v>
+        <v>2019</v>
       </c>
       <c r="E17" t="s">
         <v>26</v>
@@ -5671,7 +5671,7 @@
         <v>73</v>
       </c>
       <c r="G17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s">
         <v>90</v>
@@ -5680,71 +5680,71 @@
         <v>29</v>
       </c>
       <c r="J17" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
-        <v>150</v>
+      <c r="A18" t="s">
+        <v>319</v>
       </c>
       <c r="B18" t="s">
-        <v>179</v>
+        <v>330</v>
       </c>
       <c r="C18" t="s">
-        <v>155</v>
+        <v>320</v>
       </c>
       <c r="D18">
-        <v>2005</v>
+        <v>2020</v>
       </c>
       <c r="E18" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F18" t="s">
         <v>73</v>
       </c>
       <c r="G18" t="s">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s">
         <v>29</v>
       </c>
       <c r="J18" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K18" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="L18" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>331</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>320</v>
       </c>
       <c r="D19">
-        <v>2006</v>
+        <v>2021</v>
       </c>
       <c r="E19" t="s">
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G19" t="s">
         <v>80</v>
@@ -5756,27 +5756,27 @@
         <v>29</v>
       </c>
       <c r="J19" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K19" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L19" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>22</v>
+      <c r="A20" s="18" t="s">
+        <v>319</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>332</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>321</v>
       </c>
       <c r="D20">
-        <v>2006</v>
+        <v>2017</v>
       </c>
       <c r="E20" t="s">
         <v>26</v>
@@ -5794,33 +5794,33 @@
         <v>29</v>
       </c>
       <c r="J20" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K20" t="s">
-        <v>81</v>
+        <v>339</v>
       </c>
       <c r="L20" t="s">
-        <v>81</v>
+        <v>338</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>22</v>
+      <c r="A21" s="18" t="s">
+        <v>319</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>333</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>321</v>
       </c>
       <c r="D21">
-        <v>2006</v>
+        <v>2018</v>
       </c>
       <c r="E21" t="s">
         <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G21" t="s">
         <v>80</v>
@@ -5832,33 +5832,33 @@
         <v>29</v>
       </c>
       <c r="J21" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K21" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L21" t="s">
-        <v>81</v>
+        <v>339</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>334</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>321</v>
       </c>
       <c r="D22">
-        <v>2006</v>
+        <v>2019</v>
       </c>
       <c r="E22" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G22" t="s">
         <v>80</v>
@@ -5870,33 +5870,33 @@
         <v>29</v>
       </c>
       <c r="J22" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K22" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L22" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>319</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>335</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>321</v>
       </c>
       <c r="D23">
-        <v>2006</v>
+        <v>2020</v>
       </c>
       <c r="E23" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G23" t="s">
         <v>80</v>
@@ -5908,27 +5908,27 @@
         <v>29</v>
       </c>
       <c r="J23" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K23" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L23" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>336</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>321</v>
       </c>
       <c r="D24">
-        <v>2006</v>
+        <v>2021</v>
       </c>
       <c r="E24" t="s">
         <v>26</v>
@@ -5937,115 +5937,115 @@
         <v>73</v>
       </c>
       <c r="G24" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I24" t="s">
         <v>29</v>
       </c>
       <c r="J24" t="s">
-        <v>176</v>
+        <v>29</v>
       </c>
       <c r="K24" t="s">
         <v>47</v>
       </c>
       <c r="L24" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>82</v>
+      <c r="A25" s="18" t="s">
+        <v>344</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>352</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>341</v>
       </c>
       <c r="D25">
-        <v>2006</v>
+        <v>2018</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F25" t="s">
         <v>73</v>
       </c>
       <c r="G25" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I25" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J25" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s">
-        <v>47</v>
+        <v>361</v>
       </c>
       <c r="L25" t="s">
-        <v>115</v>
+        <v>363</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="B26" t="s">
-        <v>109</v>
+        <v>359</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>341</v>
       </c>
       <c r="D26">
-        <v>2006</v>
+        <v>2019</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F26" t="s">
         <v>73</v>
       </c>
       <c r="G26" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I26" t="s">
         <v>29</v>
       </c>
       <c r="J26" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L26" t="s">
-        <v>47</v>
+        <v>361</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>117</v>
+        <v>344</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>360</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>341</v>
       </c>
       <c r="D27">
-        <v>2006</v>
+        <v>2020</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F27" t="s">
         <v>73</v>
@@ -6057,106 +6057,106 @@
         <v>90</v>
       </c>
       <c r="I27" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J27" t="s">
         <v>90</v>
       </c>
       <c r="K27" t="s">
+        <v>362</v>
+      </c>
+      <c r="L27" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28">
+        <v>2005</v>
+      </c>
+      <c r="E28" t="s">
+        <v>26</v>
+      </c>
+      <c r="F28" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" t="s">
+        <v>90</v>
+      </c>
+      <c r="I28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J28" t="s">
+        <v>90</v>
+      </c>
+      <c r="K28" t="s">
         <v>126</v>
       </c>
-      <c r="L27" t="s">
+      <c r="L28" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="B28" t="s">
-        <v>141</v>
-      </c>
-      <c r="C28" t="s">
-        <v>129</v>
-      </c>
-      <c r="D28">
-        <v>2006</v>
-      </c>
-      <c r="E28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" t="s">
-        <v>73</v>
-      </c>
-      <c r="G28" t="s">
-        <v>114</v>
-      </c>
-      <c r="H28" t="s">
-        <v>29</v>
-      </c>
-      <c r="I28" t="s">
-        <v>29</v>
-      </c>
-      <c r="J28" t="s">
-        <v>176</v>
-      </c>
-      <c r="K28" t="s">
-        <v>45</v>
-      </c>
-      <c r="L28" t="s">
-        <v>45</v>
-      </c>
-    </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="18" t="s">
-        <v>127</v>
+      <c r="A29" t="s">
+        <v>117</v>
       </c>
       <c r="B29" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="D29">
         <v>2006</v>
       </c>
       <c r="E29" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F29" t="s">
         <v>73</v>
       </c>
       <c r="G29" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s">
         <v>29</v>
       </c>
       <c r="J29" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L29" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
-        <v>127</v>
+      <c r="A30" t="s">
+        <v>117</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D30">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="E30" t="s">
         <v>26</v>
@@ -6165,36 +6165,36 @@
         <v>73</v>
       </c>
       <c r="G30" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I30" t="s">
         <v>29</v>
       </c>
       <c r="J30" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L30" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B31" t="s">
-        <v>178</v>
+        <v>221</v>
       </c>
       <c r="C31" t="s">
-        <v>154</v>
+        <v>200</v>
       </c>
       <c r="D31">
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="E31" t="s">
         <v>26</v>
@@ -6203,10 +6203,10 @@
         <v>73</v>
       </c>
       <c r="G31" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H31" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I31" t="s">
         <v>29</v>
@@ -6215,33 +6215,33 @@
         <v>90</v>
       </c>
       <c r="K31" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L31" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B32" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="C32" t="s">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="D32">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="E32" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F32" t="s">
         <v>73</v>
       </c>
       <c r="G32" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="H32" t="s">
         <v>29</v>
@@ -6253,36 +6253,36 @@
         <v>90</v>
       </c>
       <c r="K32" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="L32" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>22</v>
+      <c r="A33" s="18" t="s">
+        <v>199</v>
       </c>
       <c r="B33" t="s">
-        <v>49</v>
+        <v>223</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>200</v>
       </c>
       <c r="D33">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="E33" t="s">
         <v>26</v>
       </c>
       <c r="F33" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H33" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I33" t="s">
         <v>29</v>
@@ -6291,36 +6291,36 @@
         <v>90</v>
       </c>
       <c r="K33" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="L33" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>22</v>
+      <c r="A34" s="18" t="s">
+        <v>199</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>224</v>
       </c>
       <c r="C34" t="s">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="D34">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="E34" t="s">
         <v>26</v>
       </c>
       <c r="F34" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G34" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H34" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I34" t="s">
         <v>29</v>
@@ -6329,36 +6329,36 @@
         <v>90</v>
       </c>
       <c r="K34" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="L34" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>22</v>
+      <c r="A35" s="18" t="s">
+        <v>199</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>225</v>
       </c>
       <c r="C35" t="s">
-        <v>61</v>
+        <v>200</v>
       </c>
       <c r="D35">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="E35" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G35" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H35" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I35" t="s">
         <v>29</v>
@@ -6367,36 +6367,36 @@
         <v>90</v>
       </c>
       <c r="K35" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="L35" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>22</v>
+      <c r="A36" s="18" t="s">
+        <v>199</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>226</v>
       </c>
       <c r="C36" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="D36">
-        <v>2007</v>
+        <v>2016</v>
       </c>
       <c r="E36" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G36" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H36" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I36" t="s">
         <v>29</v>
@@ -6405,24 +6405,24 @@
         <v>90</v>
       </c>
       <c r="K36" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="L36" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>82</v>
+      <c r="A37" s="18" t="s">
+        <v>199</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
+        <v>256</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="D37">
-        <v>2007</v>
+        <v>2017</v>
       </c>
       <c r="E37" t="s">
         <v>26</v>
@@ -6440,27 +6440,27 @@
         <v>29</v>
       </c>
       <c r="J37" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L37" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>82</v>
+      <c r="A38" s="18" t="s">
+        <v>199</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>227</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="D38">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="E38" t="s">
         <v>26</v>
@@ -6469,7 +6469,7 @@
         <v>73</v>
       </c>
       <c r="G38" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="H38" t="s">
         <v>29</v>
@@ -6478,27 +6478,27 @@
         <v>29</v>
       </c>
       <c r="J38" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="L38" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>82</v>
+      <c r="A39" s="18" t="s">
+        <v>199</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>228</v>
       </c>
       <c r="C39" t="s">
-        <v>85</v>
+        <v>201</v>
       </c>
       <c r="D39">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="E39" t="s">
         <v>26</v>
@@ -6507,7 +6507,7 @@
         <v>73</v>
       </c>
       <c r="G39" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="H39" t="s">
         <v>29</v>
@@ -6516,27 +6516,27 @@
         <v>29</v>
       </c>
       <c r="J39" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="L39" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>117</v>
+      <c r="A40" s="18" t="s">
+        <v>199</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>229</v>
       </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>201</v>
       </c>
       <c r="D40">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="E40" t="s">
         <v>26</v>
@@ -6545,10 +6545,10 @@
         <v>73</v>
       </c>
       <c r="G40" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="H40" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I40" t="s">
         <v>29</v>
@@ -6557,33 +6557,33 @@
         <v>90</v>
       </c>
       <c r="K40" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="L40" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="18" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="D41">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="E41" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F41" t="s">
         <v>73</v>
       </c>
       <c r="G41" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="H41" t="s">
         <v>29</v>
@@ -6592,36 +6592,36 @@
         <v>29</v>
       </c>
       <c r="J41" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="L41" t="s">
-        <v>45</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="18" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>231</v>
       </c>
       <c r="C42" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="D42">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="E42" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F42" t="s">
         <v>73</v>
       </c>
       <c r="G42" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="H42" t="s">
         <v>29</v>
@@ -6630,27 +6630,27 @@
         <v>29</v>
       </c>
       <c r="J42" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="L42" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="18" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="B43" t="s">
-        <v>148</v>
+        <v>232</v>
       </c>
       <c r="C43" t="s">
-        <v>128</v>
+        <v>201</v>
       </c>
       <c r="D43">
-        <v>2007</v>
+        <v>2016</v>
       </c>
       <c r="E43" t="s">
         <v>26</v>
@@ -6659,7 +6659,7 @@
         <v>73</v>
       </c>
       <c r="G43" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="H43" t="s">
         <v>29</v>
@@ -6668,33 +6668,33 @@
         <v>29</v>
       </c>
       <c r="J43" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="L43" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="18" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B44" t="s">
-        <v>185</v>
+        <v>257</v>
       </c>
       <c r="C44" t="s">
-        <v>157</v>
+        <v>201</v>
       </c>
       <c r="D44">
-        <v>2007</v>
+        <v>2017</v>
       </c>
       <c r="E44" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G44" t="s">
         <v>197</v>
@@ -6716,169 +6716,169 @@
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>22</v>
+      <c r="A45" s="18" t="s">
+        <v>199</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>233</v>
       </c>
       <c r="C45" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="D45">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="E45" t="s">
         <v>26</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G45" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H45" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I45" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J45" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K45" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="L45" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>22</v>
+      <c r="A46" s="18" t="s">
+        <v>199</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>234</v>
       </c>
       <c r="C46" t="s">
-        <v>55</v>
+        <v>202</v>
       </c>
       <c r="D46">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="E46" t="s">
         <v>26</v>
       </c>
       <c r="F46" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G46" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H46" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I46" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J46" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K46" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="L46" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
-        <v>22</v>
+        <v>199</v>
       </c>
       <c r="B47" t="s">
-        <v>64</v>
+        <v>235</v>
       </c>
       <c r="C47" t="s">
-        <v>61</v>
+        <v>202</v>
       </c>
       <c r="D47">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="E47" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="G47" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H47" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I47" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J47" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K47" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="L47" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>22</v>
+        <v>199</v>
       </c>
       <c r="B48" t="s">
-        <v>69</v>
+        <v>236</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>202</v>
       </c>
       <c r="D48">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="E48" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F48" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G48" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H48" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I48" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J48" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K48" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="L48" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>237</v>
       </c>
       <c r="C49" t="s">
-        <v>83</v>
+        <v>202</v>
       </c>
       <c r="D49">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="E49" t="s">
         <v>26</v>
@@ -6887,36 +6887,36 @@
         <v>73</v>
       </c>
       <c r="G49" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="H49" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="I49" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J49" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="K49" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="L49" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="B50" t="s">
-        <v>104</v>
+        <v>238</v>
       </c>
       <c r="C50" t="s">
-        <v>84</v>
+        <v>202</v>
       </c>
       <c r="D50">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="E50" t="s">
         <v>26</v>
@@ -6925,36 +6925,36 @@
         <v>73</v>
       </c>
       <c r="G50" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="H50" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="I50" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J50" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="K50" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="L50" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="B51" t="s">
-        <v>111</v>
+        <v>258</v>
       </c>
       <c r="C51" t="s">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="D51">
-        <v>2008</v>
+        <v>2017</v>
       </c>
       <c r="E51" t="s">
         <v>26</v>
@@ -6963,112 +6963,112 @@
         <v>73</v>
       </c>
       <c r="G51" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="H51" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="I51" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J51" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="K51" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="L51" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="B52" t="s">
-        <v>143</v>
+        <v>239</v>
       </c>
       <c r="C52" t="s">
-        <v>129</v>
+        <v>203</v>
       </c>
       <c r="D52">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="E52" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F52" t="s">
         <v>73</v>
       </c>
       <c r="G52" t="s">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="H52" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I52" t="s">
         <v>29</v>
       </c>
       <c r="J52" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L52" t="s">
-        <v>47</v>
+        <v>262</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="B53" t="s">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="C53" t="s">
-        <v>130</v>
+        <v>203</v>
       </c>
       <c r="D53">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="E53" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F53" t="s">
         <v>73</v>
       </c>
       <c r="G53" t="s">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="H53" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I53" t="s">
         <v>29</v>
       </c>
       <c r="J53" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K53" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L53" t="s">
-        <v>115</v>
+        <v>262</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
-        <v>127</v>
+        <v>199</v>
       </c>
       <c r="B54" t="s">
-        <v>149</v>
+        <v>241</v>
       </c>
       <c r="C54" t="s">
-        <v>128</v>
+        <v>203</v>
       </c>
       <c r="D54">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="E54" t="s">
         <v>26</v>
@@ -7077,48 +7077,48 @@
         <v>73</v>
       </c>
       <c r="G54" t="s">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="H54" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I54" t="s">
         <v>29</v>
       </c>
       <c r="J54" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L54" t="s">
-        <v>115</v>
+        <v>262</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B55" t="s">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="C55" t="s">
-        <v>156</v>
+        <v>203</v>
       </c>
       <c r="D55">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="E55" t="s">
         <v>26</v>
       </c>
       <c r="F55" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G55" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="H55" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I55" t="s">
         <v>29</v>
@@ -7127,36 +7127,36 @@
         <v>90</v>
       </c>
       <c r="K55" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="L55" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B56" t="s">
-        <v>186</v>
+        <v>243</v>
       </c>
       <c r="C56" t="s">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="D56">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="E56" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F56" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G56" t="s">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="H56" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I56" t="s">
         <v>29</v>
@@ -7165,24 +7165,24 @@
         <v>90</v>
       </c>
       <c r="K56" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="L56" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B57" t="s">
-        <v>189</v>
+        <v>244</v>
       </c>
       <c r="C57" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="D57">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="E57" t="s">
         <v>26</v>
@@ -7191,10 +7191,10 @@
         <v>73</v>
       </c>
       <c r="G57" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="H57" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I57" t="s">
         <v>29</v>
@@ -7203,24 +7203,24 @@
         <v>90</v>
       </c>
       <c r="K57" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="L57" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B58" t="s">
-        <v>193</v>
+        <v>259</v>
       </c>
       <c r="C58" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="D58">
-        <v>2008</v>
+        <v>2017</v>
       </c>
       <c r="E58" t="s">
         <v>26</v>
@@ -7229,10 +7229,10 @@
         <v>73</v>
       </c>
       <c r="G58" t="s">
-        <v>197</v>
+        <v>263</v>
       </c>
       <c r="H58" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I58" t="s">
         <v>29</v>
@@ -7241,24 +7241,24 @@
         <v>90</v>
       </c>
       <c r="K58" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="L58" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="B59" t="s">
-        <v>98</v>
+        <v>245</v>
       </c>
       <c r="C59" t="s">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="D59">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="E59" t="s">
         <v>26</v>
@@ -7267,36 +7267,36 @@
         <v>73</v>
       </c>
       <c r="G59" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I59" t="s">
         <v>29</v>
       </c>
       <c r="J59" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L59" t="s">
-        <v>115</v>
+        <v>262</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="B60" t="s">
-        <v>105</v>
+        <v>246</v>
       </c>
       <c r="C60" t="s">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="D60">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="E60" t="s">
         <v>26</v>
@@ -7305,36 +7305,36 @@
         <v>73</v>
       </c>
       <c r="G60" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I60" t="s">
         <v>29</v>
       </c>
       <c r="J60" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L60" t="s">
-        <v>115</v>
+        <v>262</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="B61" t="s">
-        <v>112</v>
+        <v>247</v>
       </c>
       <c r="C61" t="s">
-        <v>85</v>
+        <v>204</v>
       </c>
       <c r="D61">
-        <v>2009</v>
+        <v>2013</v>
       </c>
       <c r="E61" t="s">
         <v>26</v>
@@ -7343,48 +7343,48 @@
         <v>73</v>
       </c>
       <c r="G61" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H61" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I61" t="s">
         <v>29</v>
       </c>
       <c r="J61" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K61" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L61" t="s">
-        <v>47</v>
+        <v>262</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B62" t="s">
-        <v>182</v>
+        <v>248</v>
       </c>
       <c r="C62" t="s">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="D62">
-        <v>2009</v>
+        <v>2014</v>
       </c>
       <c r="E62" t="s">
         <v>26</v>
       </c>
       <c r="F62" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G62" t="s">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I62" t="s">
         <v>29</v>
@@ -7393,24 +7393,24 @@
         <v>90</v>
       </c>
       <c r="K62" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="L62" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B63" t="s">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="C63" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="D63">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="E63" t="s">
         <v>26</v>
@@ -7419,10 +7419,10 @@
         <v>73</v>
       </c>
       <c r="G63" t="s">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I63" t="s">
         <v>29</v>
@@ -7431,24 +7431,24 @@
         <v>90</v>
       </c>
       <c r="K63" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="L63" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B64" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="C64" t="s">
-        <v>159</v>
+        <v>204</v>
       </c>
       <c r="D64">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="E64" t="s">
         <v>26</v>
@@ -7457,10 +7457,10 @@
         <v>73</v>
       </c>
       <c r="G64" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I64" t="s">
         <v>29</v>
@@ -7469,24 +7469,24 @@
         <v>90</v>
       </c>
       <c r="K64" t="s">
-        <v>197</v>
+        <v>126</v>
       </c>
       <c r="L64" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="B65" t="s">
-        <v>99</v>
+        <v>260</v>
       </c>
       <c r="C65" t="s">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="D65">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="E65" t="s">
         <v>26</v>
@@ -7495,36 +7495,36 @@
         <v>73</v>
       </c>
       <c r="G65" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I65" t="s">
         <v>29</v>
       </c>
       <c r="J65" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K65" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L65" t="s">
-        <v>47</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>251</v>
       </c>
       <c r="C66" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="D66">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E66" t="s">
         <v>26</v>
@@ -7533,36 +7533,36 @@
         <v>73</v>
       </c>
       <c r="G66" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="H66" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="I66" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J66" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="K66" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="L66" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="B67" t="s">
-        <v>113</v>
+        <v>252</v>
       </c>
       <c r="C67" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="D67">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="E67" t="s">
         <v>26</v>
@@ -7571,112 +7571,112 @@
         <v>73</v>
       </c>
       <c r="G67" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="H67" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="I67" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J67" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="K67" t="s">
-        <v>115</v>
+        <v>73</v>
       </c>
       <c r="L67" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B68" t="s">
-        <v>183</v>
+        <v>253</v>
       </c>
       <c r="C68" t="s">
-        <v>156</v>
+        <v>205</v>
       </c>
       <c r="D68">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="E68" t="s">
         <v>26</v>
       </c>
       <c r="F68" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G68" t="s">
-        <v>198</v>
+        <v>73</v>
       </c>
       <c r="H68" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="I68" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J68" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K68" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="L68" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B69" t="s">
-        <v>187</v>
+        <v>254</v>
       </c>
       <c r="C69" t="s">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="D69">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="E69" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F69" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G69" t="s">
-        <v>198</v>
+        <v>73</v>
       </c>
       <c r="H69" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="I69" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J69" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K69" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="L69" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B70" t="s">
-        <v>191</v>
+        <v>255</v>
       </c>
       <c r="C70" t="s">
-        <v>158</v>
+        <v>205</v>
       </c>
       <c r="D70">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="E70" t="s">
         <v>26</v>
@@ -7685,36 +7685,36 @@
         <v>73</v>
       </c>
       <c r="G70" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="H70" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="I70" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J70" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K70" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="L70" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B71" t="s">
-        <v>195</v>
+        <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>159</v>
+        <v>205</v>
       </c>
       <c r="D71">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="E71" t="s">
         <v>26</v>
@@ -7723,22 +7723,22 @@
         <v>73</v>
       </c>
       <c r="G71" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="H71" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="I71" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J71" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K71" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="L71" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
@@ -7746,25 +7746,25 @@
         <v>150</v>
       </c>
       <c r="B72" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="C72" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D72">
-        <v>2011</v>
+        <v>2005</v>
       </c>
       <c r="E72" t="s">
         <v>26</v>
       </c>
       <c r="F72" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G72" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I72" t="s">
         <v>29</v>
@@ -7773,10 +7773,10 @@
         <v>90</v>
       </c>
       <c r="K72" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="L72" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
@@ -7784,25 +7784,25 @@
         <v>150</v>
       </c>
       <c r="B73" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C73" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D73">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="E73" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F73" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="G73" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="H73" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I73" t="s">
         <v>29</v>
@@ -7811,10 +7811,10 @@
         <v>90</v>
       </c>
       <c r="K73" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="L73" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
@@ -7822,22 +7822,22 @@
         <v>150</v>
       </c>
       <c r="B74" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="C74" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D74">
-        <v>2011</v>
+        <v>2005</v>
       </c>
       <c r="E74" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F74" t="s">
         <v>73</v>
       </c>
       <c r="G74" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H74" t="s">
         <v>29</v>
@@ -7860,16 +7860,16 @@
         <v>150</v>
       </c>
       <c r="B75" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="C75" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D75">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="E75" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F75" t="s">
         <v>73</v>
@@ -7895,25 +7895,25 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="B76" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="C76" t="s">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="D76">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="E76" t="s">
         <v>26</v>
       </c>
       <c r="F76" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G76" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="H76" t="s">
         <v>29</v>
@@ -7925,33 +7925,33 @@
         <v>90</v>
       </c>
       <c r="K76" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="L76" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="B77" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="C77" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="D77">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="E77" t="s">
         <v>26</v>
       </c>
       <c r="F77" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G77" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H77" t="s">
         <v>29</v>
@@ -7971,51 +7971,51 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="8" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="B78" t="s">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="C78" t="s">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="D78">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E78" t="s">
         <v>26</v>
       </c>
       <c r="F78" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G78" t="s">
-        <v>73</v>
+        <v>198</v>
       </c>
       <c r="H78" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I78" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J78" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K78" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="L78" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="B79" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="C79" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="D79">
         <v>2011</v>
@@ -8024,13 +8024,13 @@
         <v>26</v>
       </c>
       <c r="F79" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G79" t="s">
-        <v>263</v>
+        <v>197</v>
       </c>
       <c r="H79" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I79" t="s">
         <v>29</v>
@@ -8039,36 +8039,36 @@
         <v>90</v>
       </c>
       <c r="K79" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="L79" t="s">
-        <v>262</v>
+        <v>197</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="B80" t="s">
-        <v>245</v>
+        <v>185</v>
       </c>
       <c r="C80" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="D80">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="E80" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F80" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G80" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="H80" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I80" t="s">
         <v>29</v>
@@ -8077,74 +8077,74 @@
         <v>90</v>
       </c>
       <c r="K80" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="L80" t="s">
-        <v>262</v>
+        <v>197</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
-        <v>264</v>
+        <v>150</v>
       </c>
       <c r="B81" t="s">
-        <v>276</v>
+        <v>186</v>
       </c>
       <c r="C81" t="s">
-        <v>277</v>
+        <v>157</v>
       </c>
       <c r="D81">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="E81" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F81" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G81" t="s">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="H81" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I81" t="s">
         <v>29</v>
       </c>
       <c r="J81" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K81" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="L81" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
-        <v>264</v>
+        <v>150</v>
       </c>
       <c r="B82" t="s">
-        <v>283</v>
+        <v>187</v>
       </c>
       <c r="C82" t="s">
-        <v>284</v>
+        <v>157</v>
       </c>
       <c r="D82">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E82" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F82" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G82" t="s">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="H82" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I82" t="s">
         <v>29</v>
@@ -8153,33 +8153,33 @@
         <v>90</v>
       </c>
       <c r="K82" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="L82" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="B83" t="s">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="C83" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="D83">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E83" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F83" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="G83" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="H83" t="s">
         <v>29</v>
@@ -8191,24 +8191,24 @@
         <v>90</v>
       </c>
       <c r="K83" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="L83" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="B84" t="s">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="C84" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
       <c r="D84">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="E84" t="s">
         <v>26</v>
@@ -8237,16 +8237,16 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="B85" t="s">
-        <v>234</v>
+        <v>190</v>
       </c>
       <c r="C85" t="s">
-        <v>202</v>
+        <v>158</v>
       </c>
       <c r="D85">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="E85" t="s">
         <v>26</v>
@@ -8255,36 +8255,36 @@
         <v>73</v>
       </c>
       <c r="G85" t="s">
-        <v>73</v>
+        <v>198</v>
       </c>
       <c r="H85" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I85" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J85" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K85" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="L85" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="8" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="B86" t="s">
-        <v>240</v>
+        <v>191</v>
       </c>
       <c r="C86" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="D86">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E86" t="s">
         <v>26</v>
@@ -8293,10 +8293,10 @@
         <v>73</v>
       </c>
       <c r="G86" t="s">
-        <v>263</v>
+        <v>197</v>
       </c>
       <c r="H86" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I86" t="s">
         <v>29</v>
@@ -8305,24 +8305,24 @@
         <v>90</v>
       </c>
       <c r="K86" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="L86" t="s">
-        <v>262</v>
+        <v>197</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="B87" t="s">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="C87" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="D87">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E87" t="s">
         <v>26</v>
@@ -8331,10 +8331,10 @@
         <v>73</v>
       </c>
       <c r="G87" t="s">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="H87" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I87" t="s">
         <v>29</v>
@@ -8343,24 +8343,24 @@
         <v>90</v>
       </c>
       <c r="K87" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="L87" t="s">
-        <v>262</v>
+        <v>197</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="B88" t="s">
-        <v>251</v>
+        <v>193</v>
       </c>
       <c r="C88" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="D88">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="E88" t="s">
         <v>26</v>
@@ -8369,36 +8369,36 @@
         <v>73</v>
       </c>
       <c r="G88" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="H88" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I88" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J88" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K88" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="L88" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
-        <v>264</v>
+        <v>150</v>
       </c>
       <c r="B89" t="s">
-        <v>278</v>
+        <v>194</v>
       </c>
       <c r="C89" t="s">
-        <v>277</v>
+        <v>159</v>
       </c>
       <c r="D89">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="E89" t="s">
         <v>26</v>
@@ -8407,36 +8407,36 @@
         <v>73</v>
       </c>
       <c r="G89" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="H89" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I89" t="s">
         <v>29</v>
       </c>
       <c r="J89" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K89" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="L89" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
-        <v>264</v>
+        <v>150</v>
       </c>
       <c r="B90" t="s">
-        <v>285</v>
+        <v>195</v>
       </c>
       <c r="C90" t="s">
-        <v>284</v>
+        <v>159</v>
       </c>
       <c r="D90">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="E90" t="s">
         <v>26</v>
@@ -8445,10 +8445,10 @@
         <v>73</v>
       </c>
       <c r="G90" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="H90" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I90" t="s">
         <v>29</v>
@@ -8457,24 +8457,24 @@
         <v>90</v>
       </c>
       <c r="K90" t="s">
-        <v>45</v>
+        <v>197</v>
       </c>
       <c r="L90" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="8" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="B91" t="s">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="C91" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="D91">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="E91" t="s">
         <v>26</v>
@@ -8483,7 +8483,7 @@
         <v>73</v>
       </c>
       <c r="G91" t="s">
-        <v>114</v>
+        <v>197</v>
       </c>
       <c r="H91" t="s">
         <v>29</v>
@@ -8495,24 +8495,24 @@
         <v>90</v>
       </c>
       <c r="K91" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
       <c r="L91" t="s">
-        <v>126</v>
+        <v>197</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="8" t="s">
-        <v>199</v>
+        <v>414</v>
       </c>
       <c r="B92" t="s">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="C92" t="s">
-        <v>201</v>
+        <v>384</v>
       </c>
       <c r="D92">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="E92" t="s">
         <v>26</v>
@@ -8521,36 +8521,36 @@
         <v>73</v>
       </c>
       <c r="G92" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="H92" t="s">
         <v>29</v>
       </c>
       <c r="I92" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J92" t="s">
         <v>90</v>
       </c>
       <c r="K92" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="L92" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="8" t="s">
-        <v>199</v>
+        <v>414</v>
       </c>
       <c r="B93" t="s">
-        <v>235</v>
+        <v>391</v>
       </c>
       <c r="C93" t="s">
-        <v>202</v>
+        <v>384</v>
       </c>
       <c r="D93">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="E93" t="s">
         <v>26</v>
@@ -8559,36 +8559,36 @@
         <v>73</v>
       </c>
       <c r="G93" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="H93" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I93" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="J93" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K93" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L93" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="8" t="s">
-        <v>199</v>
+        <v>414</v>
       </c>
       <c r="B94" t="s">
-        <v>241</v>
+        <v>397</v>
       </c>
       <c r="C94" t="s">
-        <v>203</v>
+        <v>384</v>
       </c>
       <c r="D94">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="E94" t="s">
         <v>26</v>
@@ -8597,10 +8597,10 @@
         <v>73</v>
       </c>
       <c r="G94" t="s">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="H94" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I94" t="s">
         <v>29</v>
@@ -8609,24 +8609,24 @@
         <v>90</v>
       </c>
       <c r="K94" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="L94" t="s">
-        <v>262</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="8" t="s">
-        <v>199</v>
+        <v>414</v>
       </c>
       <c r="B95" t="s">
-        <v>247</v>
+        <v>398</v>
       </c>
       <c r="C95" t="s">
-        <v>204</v>
+        <v>384</v>
       </c>
       <c r="D95">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="E95" t="s">
         <v>26</v>
@@ -8635,10 +8635,10 @@
         <v>73</v>
       </c>
       <c r="G95" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H95" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I95" t="s">
         <v>29</v>
@@ -8647,24 +8647,24 @@
         <v>90</v>
       </c>
       <c r="K95" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="L95" t="s">
-        <v>262</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="8" t="s">
-        <v>199</v>
+        <v>414</v>
       </c>
       <c r="B96" t="s">
-        <v>252</v>
+        <v>399</v>
       </c>
       <c r="C96" t="s">
-        <v>205</v>
+        <v>384</v>
       </c>
       <c r="D96">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="E96" t="s">
         <v>26</v>
@@ -8673,36 +8673,36 @@
         <v>73</v>
       </c>
       <c r="G96" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="H96" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I96" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J96" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K96" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L96" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="8" t="s">
-        <v>264</v>
+        <v>415</v>
       </c>
       <c r="B97" t="s">
-        <v>279</v>
+        <v>392</v>
       </c>
       <c r="C97" t="s">
-        <v>277</v>
+        <v>385</v>
       </c>
       <c r="D97">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="E97" t="s">
         <v>26</v>
@@ -8711,36 +8711,36 @@
         <v>73</v>
       </c>
       <c r="G97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H97" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I97" t="s">
         <v>29</v>
       </c>
       <c r="J97" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K97" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L97" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="8" t="s">
-        <v>264</v>
+        <v>415</v>
       </c>
       <c r="B98" t="s">
-        <v>286</v>
+        <v>393</v>
       </c>
       <c r="C98" t="s">
-        <v>284</v>
+        <v>385</v>
       </c>
       <c r="D98">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="E98" t="s">
         <v>26</v>
@@ -8749,10 +8749,10 @@
         <v>73</v>
       </c>
       <c r="G98" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H98" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I98" t="s">
         <v>29</v>
@@ -8761,24 +8761,24 @@
         <v>90</v>
       </c>
       <c r="K98" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="L98" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="8" t="s">
-        <v>199</v>
+        <v>415</v>
       </c>
       <c r="B99" t="s">
-        <v>224</v>
+        <v>394</v>
       </c>
       <c r="C99" t="s">
-        <v>200</v>
+        <v>385</v>
       </c>
       <c r="D99">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="E99" t="s">
         <v>26</v>
@@ -8787,7 +8787,7 @@
         <v>73</v>
       </c>
       <c r="G99" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="H99" t="s">
         <v>29</v>
@@ -8799,24 +8799,24 @@
         <v>90</v>
       </c>
       <c r="K99" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="L99" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="8" t="s">
-        <v>199</v>
+        <v>415</v>
       </c>
       <c r="B100" t="s">
-        <v>230</v>
+        <v>395</v>
       </c>
       <c r="C100" t="s">
-        <v>201</v>
+        <v>385</v>
       </c>
       <c r="D100">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="E100" t="s">
         <v>26</v>
@@ -8825,7 +8825,7 @@
         <v>73</v>
       </c>
       <c r="G100" t="s">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="H100" t="s">
         <v>29</v>
@@ -8837,24 +8837,24 @@
         <v>90</v>
       </c>
       <c r="K100" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="L100" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="8" t="s">
-        <v>199</v>
+        <v>415</v>
       </c>
       <c r="B101" t="s">
-        <v>236</v>
+        <v>396</v>
       </c>
       <c r="C101" t="s">
-        <v>202</v>
+        <v>385</v>
       </c>
       <c r="D101">
-        <v>2014</v>
+        <v>2023</v>
       </c>
       <c r="E101" t="s">
         <v>26</v>
@@ -8863,171 +8863,171 @@
         <v>73</v>
       </c>
       <c r="G101" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H101" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I101" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J101" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K101" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L101" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="8" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="B102" t="s">
-        <v>242</v>
+        <v>141</v>
       </c>
       <c r="C102" t="s">
-        <v>203</v>
+        <v>129</v>
       </c>
       <c r="D102">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="E102" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F102" t="s">
         <v>73</v>
       </c>
       <c r="G102" t="s">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="H102" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I102" t="s">
         <v>29</v>
       </c>
       <c r="J102" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K102" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="L102" t="s">
-        <v>262</v>
+        <v>45</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="B103" t="s">
-        <v>248</v>
+        <v>142</v>
       </c>
       <c r="C103" t="s">
-        <v>204</v>
+        <v>129</v>
       </c>
       <c r="D103">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="E103" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F103" t="s">
         <v>73</v>
       </c>
       <c r="G103" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H103" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I103" t="s">
         <v>29</v>
       </c>
       <c r="J103" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K103" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="L103" t="s">
-        <v>262</v>
+        <v>45</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="B104" t="s">
-        <v>253</v>
+        <v>143</v>
       </c>
       <c r="C104" t="s">
-        <v>205</v>
+        <v>129</v>
       </c>
       <c r="D104">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="E104" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F104" t="s">
         <v>73</v>
       </c>
       <c r="G104" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="H104" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I104" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J104" t="s">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="K104" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="L104" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
-        <v>264</v>
+        <v>127</v>
       </c>
       <c r="B105" t="s">
-        <v>280</v>
+        <v>144</v>
       </c>
       <c r="C105" t="s">
-        <v>277</v>
+        <v>130</v>
       </c>
       <c r="D105">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="E105" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F105" t="s">
         <v>73</v>
       </c>
       <c r="G105" t="s">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="H105" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I105" t="s">
         <v>29</v>
       </c>
       <c r="J105" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="K105" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="L105" t="s">
         <v>47</v>
@@ -9035,92 +9035,92 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
-        <v>264</v>
+        <v>127</v>
       </c>
       <c r="B106" t="s">
-        <v>287</v>
+        <v>145</v>
       </c>
       <c r="C106" t="s">
-        <v>284</v>
+        <v>130</v>
       </c>
       <c r="D106">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="E106" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F106" t="s">
         <v>73</v>
       </c>
       <c r="G106" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H106" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I106" t="s">
         <v>29</v>
       </c>
       <c r="J106" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K106" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="L106" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
-        <v>264</v>
+        <v>127</v>
       </c>
       <c r="B107" t="s">
-        <v>290</v>
+        <v>146</v>
       </c>
       <c r="C107" t="s">
-        <v>291</v>
+        <v>130</v>
       </c>
       <c r="D107">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="E107" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F107" t="s">
         <v>73</v>
       </c>
       <c r="G107" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="H107" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I107" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J107" t="s">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="K107" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="L107" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="B108" t="s">
-        <v>225</v>
+        <v>147</v>
       </c>
       <c r="C108" t="s">
-        <v>200</v>
+        <v>128</v>
       </c>
       <c r="D108">
-        <v>2015</v>
+        <v>2006</v>
       </c>
       <c r="E108" t="s">
         <v>26</v>
@@ -9138,27 +9138,27 @@
         <v>29</v>
       </c>
       <c r="J108" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K108" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="L108" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="B109" t="s">
-        <v>231</v>
+        <v>148</v>
       </c>
       <c r="C109" t="s">
-        <v>201</v>
+        <v>128</v>
       </c>
       <c r="D109">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="E109" t="s">
         <v>26</v>
@@ -9167,7 +9167,7 @@
         <v>73</v>
       </c>
       <c r="G109" t="s">
-        <v>197</v>
+        <v>114</v>
       </c>
       <c r="H109" t="s">
         <v>29</v>
@@ -9176,27 +9176,27 @@
         <v>29</v>
       </c>
       <c r="J109" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K109" t="s">
-        <v>197</v>
+        <v>115</v>
       </c>
       <c r="L109" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
-        <v>199</v>
+        <v>127</v>
       </c>
       <c r="B110" t="s">
-        <v>237</v>
+        <v>149</v>
       </c>
       <c r="C110" t="s">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="D110">
-        <v>2015</v>
+        <v>2008</v>
       </c>
       <c r="E110" t="s">
         <v>26</v>
@@ -9205,45 +9205,45 @@
         <v>73</v>
       </c>
       <c r="G110" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="H110" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I110" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J110" t="s">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="K110" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="L110" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
-        <v>199</v>
+        <v>344</v>
       </c>
       <c r="B111" t="s">
-        <v>243</v>
+        <v>353</v>
       </c>
       <c r="C111" t="s">
-        <v>203</v>
+        <v>340</v>
       </c>
       <c r="D111">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="E111" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F111" t="s">
         <v>73</v>
       </c>
       <c r="G111" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="H111" t="s">
         <v>90</v>
@@ -9255,27 +9255,27 @@
         <v>90</v>
       </c>
       <c r="K111" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="L111" t="s">
-        <v>262</v>
+        <v>115</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
-        <v>199</v>
+        <v>344</v>
       </c>
       <c r="B112" t="s">
-        <v>249</v>
+        <v>354</v>
       </c>
       <c r="C112" t="s">
-        <v>204</v>
+        <v>340</v>
       </c>
       <c r="D112">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="E112" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F112" t="s">
         <v>73</v>
@@ -9287,68 +9287,68 @@
         <v>90</v>
       </c>
       <c r="I112" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J112" t="s">
         <v>90</v>
       </c>
       <c r="K112" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="L112" t="s">
-        <v>262</v>
+        <v>47</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
-        <v>199</v>
+        <v>344</v>
       </c>
       <c r="B113" t="s">
-        <v>254</v>
+        <v>355</v>
       </c>
       <c r="C113" t="s">
-        <v>205</v>
+        <v>340</v>
       </c>
       <c r="D113">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="E113" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F113" t="s">
         <v>73</v>
       </c>
       <c r="G113" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H113" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I113" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J113" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K113" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L113" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="8" t="s">
-        <v>264</v>
+        <v>434</v>
       </c>
       <c r="B114" t="s">
-        <v>281</v>
+        <v>447</v>
       </c>
       <c r="C114" t="s">
-        <v>277</v>
+        <v>437</v>
       </c>
       <c r="D114">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="E114" t="s">
         <v>26</v>
@@ -9357,7 +9357,7 @@
         <v>73</v>
       </c>
       <c r="G114" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H114" t="s">
         <v>90</v>
@@ -9366,27 +9366,27 @@
         <v>29</v>
       </c>
       <c r="J114" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K114" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L114" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
-        <v>264</v>
+        <v>434</v>
       </c>
       <c r="B115" t="s">
-        <v>288</v>
+        <v>448</v>
       </c>
       <c r="C115" t="s">
-        <v>284</v>
+        <v>437</v>
       </c>
       <c r="D115">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="E115" t="s">
         <v>26</v>
@@ -9395,7 +9395,7 @@
         <v>73</v>
       </c>
       <c r="G115" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="H115" t="s">
         <v>90</v>
@@ -9407,24 +9407,24 @@
         <v>90</v>
       </c>
       <c r="K115" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L115" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
-        <v>264</v>
+        <v>435</v>
       </c>
       <c r="B116" t="s">
-        <v>292</v>
+        <v>449</v>
       </c>
       <c r="C116" t="s">
-        <v>291</v>
+        <v>438</v>
       </c>
       <c r="D116">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="E116" t="s">
         <v>26</v>
@@ -9433,124 +9433,124 @@
         <v>73</v>
       </c>
       <c r="G116" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="H116" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I116" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J116" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K116" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="L116" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="8" t="s">
-        <v>318</v>
+        <v>22</v>
       </c>
       <c r="B117" t="s">
-        <v>304</v>
+        <v>43</v>
       </c>
       <c r="C117" t="s">
-        <v>298</v>
+        <v>44</v>
       </c>
       <c r="D117">
-        <v>2015</v>
+        <v>2004</v>
       </c>
       <c r="E117" t="s">
         <v>26</v>
       </c>
       <c r="F117" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G117" t="s">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="H117" t="s">
         <v>90</v>
       </c>
       <c r="I117" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J117" t="s">
         <v>90</v>
       </c>
       <c r="K117" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L117" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="8" t="s">
-        <v>318</v>
+        <v>22</v>
       </c>
       <c r="B118" t="s">
-        <v>311</v>
+        <v>46</v>
       </c>
       <c r="C118" t="s">
-        <v>299</v>
+        <v>44</v>
       </c>
       <c r="D118">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="E118" t="s">
         <v>26</v>
       </c>
       <c r="F118" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G118" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H118" t="s">
         <v>90</v>
       </c>
       <c r="I118" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J118" t="s">
         <v>90</v>
       </c>
       <c r="K118" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="L118" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B119" t="s">
-        <v>226</v>
+        <v>48</v>
       </c>
       <c r="C119" t="s">
-        <v>200</v>
+        <v>44</v>
       </c>
       <c r="D119">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="E119" t="s">
         <v>26</v>
       </c>
       <c r="F119" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G119" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H119" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I119" t="s">
         <v>29</v>
@@ -9559,36 +9559,36 @@
         <v>90</v>
       </c>
       <c r="K119" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="L119" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="8" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B120" t="s">
-        <v>232</v>
+        <v>49</v>
       </c>
       <c r="C120" t="s">
-        <v>201</v>
+        <v>44</v>
       </c>
       <c r="D120">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="E120" t="s">
         <v>26</v>
       </c>
       <c r="F120" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G120" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="H120" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I120" t="s">
         <v>29</v>
@@ -9597,62 +9597,62 @@
         <v>90</v>
       </c>
       <c r="K120" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="L120" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B121" t="s">
-        <v>238</v>
+        <v>50</v>
       </c>
       <c r="C121" t="s">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="D121">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="E121" t="s">
         <v>26</v>
       </c>
       <c r="F121" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G121" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H121" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I121" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J121" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K121" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L121" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B122" t="s">
-        <v>244</v>
+        <v>51</v>
       </c>
       <c r="C122" t="s">
-        <v>203</v>
+        <v>23</v>
       </c>
       <c r="D122">
-        <v>2016</v>
+        <v>2004</v>
       </c>
       <c r="E122" t="s">
         <v>26</v>
@@ -9661,7 +9661,7 @@
         <v>73</v>
       </c>
       <c r="G122" t="s">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="H122" t="s">
         <v>90</v>
@@ -9673,24 +9673,24 @@
         <v>90</v>
       </c>
       <c r="K122" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="L122" t="s">
-        <v>262</v>
+        <v>45</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B123" t="s">
-        <v>250</v>
+        <v>52</v>
       </c>
       <c r="C123" t="s">
-        <v>204</v>
+        <v>23</v>
       </c>
       <c r="D123">
-        <v>2016</v>
+        <v>2005</v>
       </c>
       <c r="E123" t="s">
         <v>26</v>
@@ -9711,24 +9711,24 @@
         <v>90</v>
       </c>
       <c r="K123" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="L123" t="s">
-        <v>262</v>
+        <v>45</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B124" t="s">
-        <v>255</v>
+        <v>53</v>
       </c>
       <c r="C124" t="s">
-        <v>205</v>
+        <v>23</v>
       </c>
       <c r="D124">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="E124" t="s">
         <v>26</v>
@@ -9737,45 +9737,45 @@
         <v>73</v>
       </c>
       <c r="G124" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H124" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I124" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J124" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K124" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L124" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
-        <v>264</v>
+        <v>22</v>
       </c>
       <c r="B125" t="s">
-        <v>282</v>
+        <v>54</v>
       </c>
       <c r="C125" t="s">
-        <v>277</v>
+        <v>55</v>
       </c>
       <c r="D125">
-        <v>2016</v>
+        <v>2004</v>
       </c>
       <c r="E125" t="s">
         <v>26</v>
       </c>
       <c r="F125" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G125" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H125" t="s">
         <v>90</v>
@@ -9784,33 +9784,33 @@
         <v>29</v>
       </c>
       <c r="J125" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K125" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L125" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
-        <v>264</v>
+        <v>22</v>
       </c>
       <c r="B126" t="s">
-        <v>289</v>
+        <v>56</v>
       </c>
       <c r="C126" t="s">
-        <v>284</v>
+        <v>55</v>
       </c>
       <c r="D126">
-        <v>2016</v>
+        <v>2005</v>
       </c>
       <c r="E126" t="s">
         <v>26</v>
       </c>
       <c r="F126" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G126" t="s">
         <v>80</v>
@@ -9825,150 +9825,150 @@
         <v>90</v>
       </c>
       <c r="K126" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L126" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
-        <v>264</v>
+        <v>22</v>
       </c>
       <c r="B127" t="s">
-        <v>293</v>
+        <v>57</v>
       </c>
       <c r="C127" t="s">
-        <v>291</v>
+        <v>55</v>
       </c>
       <c r="D127">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="E127" t="s">
         <v>26</v>
       </c>
       <c r="F127" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G127" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H127" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I127" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J127" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K127" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L127" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
-        <v>318</v>
+        <v>22</v>
       </c>
       <c r="B128" t="s">
-        <v>305</v>
+        <v>58</v>
       </c>
       <c r="C128" t="s">
-        <v>298</v>
+        <v>55</v>
       </c>
       <c r="D128">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="E128" t="s">
         <v>26</v>
       </c>
       <c r="F128" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G128" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="H128" t="s">
         <v>90</v>
       </c>
       <c r="I128" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J128" t="s">
         <v>90</v>
       </c>
       <c r="K128" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L128" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
-        <v>318</v>
+        <v>22</v>
       </c>
       <c r="B129" t="s">
-        <v>312</v>
+        <v>59</v>
       </c>
       <c r="C129" t="s">
-        <v>299</v>
+        <v>55</v>
       </c>
       <c r="D129">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="E129" t="s">
         <v>26</v>
       </c>
       <c r="F129" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G129" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="H129" t="s">
         <v>90</v>
       </c>
       <c r="I129" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J129" t="s">
         <v>90</v>
       </c>
       <c r="K129" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L129" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B130" t="s">
-        <v>256</v>
+        <v>60</v>
       </c>
       <c r="C130" t="s">
-        <v>200</v>
+        <v>61</v>
       </c>
       <c r="D130">
-        <v>2017</v>
+        <v>2005</v>
       </c>
       <c r="E130" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F130" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G130" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H130" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I130" t="s">
         <v>29</v>
@@ -9977,36 +9977,36 @@
         <v>90</v>
       </c>
       <c r="K130" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="L130" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B131" t="s">
-        <v>257</v>
+        <v>62</v>
       </c>
       <c r="C131" t="s">
-        <v>201</v>
+        <v>61</v>
       </c>
       <c r="D131">
-        <v>2017</v>
+        <v>2006</v>
       </c>
       <c r="E131" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F131" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G131" t="s">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="H131" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I131" t="s">
         <v>29</v>
@@ -10015,71 +10015,71 @@
         <v>90</v>
       </c>
       <c r="K131" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="L131" t="s">
-        <v>197</v>
+        <v>81</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B132" t="s">
-        <v>258</v>
+        <v>63</v>
       </c>
       <c r="C132" t="s">
-        <v>202</v>
+        <v>61</v>
       </c>
       <c r="D132">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="E132" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F132" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G132" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H132" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I132" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J132" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K132" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L132" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B133" t="s">
-        <v>259</v>
+        <v>64</v>
       </c>
       <c r="C133" t="s">
-        <v>203</v>
+        <v>61</v>
       </c>
       <c r="D133">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="E133" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F133" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="G133" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
       <c r="H133" t="s">
         <v>90</v>
@@ -10091,30 +10091,30 @@
         <v>90</v>
       </c>
       <c r="K133" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="L133" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B134" t="s">
-        <v>260</v>
+        <v>65</v>
       </c>
       <c r="C134" t="s">
-        <v>204</v>
+        <v>66</v>
       </c>
       <c r="D134">
-        <v>2017</v>
+        <v>2005</v>
       </c>
       <c r="E134" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F134" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G134" t="s">
         <v>80</v>
@@ -10129,71 +10129,71 @@
         <v>90</v>
       </c>
       <c r="K134" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="L134" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
-        <v>199</v>
+        <v>22</v>
       </c>
       <c r="B135" t="s">
-        <v>261</v>
+        <v>67</v>
       </c>
       <c r="C135" t="s">
-        <v>205</v>
+        <v>66</v>
       </c>
       <c r="D135">
-        <v>2017</v>
+        <v>2006</v>
       </c>
       <c r="E135" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F135" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G135" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H135" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="I135" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J135" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="K135" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="L135" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
-        <v>264</v>
+        <v>22</v>
       </c>
       <c r="B136" t="s">
-        <v>294</v>
+        <v>68</v>
       </c>
       <c r="C136" t="s">
-        <v>277</v>
+        <v>66</v>
       </c>
       <c r="D136">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="E136" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F136" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G136" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H136" t="s">
         <v>90</v>
@@ -10202,33 +10202,33 @@
         <v>29</v>
       </c>
       <c r="J136" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K136" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L136" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
-        <v>264</v>
+        <v>22</v>
       </c>
       <c r="B137" t="s">
-        <v>295</v>
+        <v>69</v>
       </c>
       <c r="C137" t="s">
-        <v>284</v>
+        <v>66</v>
       </c>
       <c r="D137">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="E137" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F137" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="G137" t="s">
         <v>80</v>
@@ -10243,24 +10243,24 @@
         <v>90</v>
       </c>
       <c r="K137" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="L137" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="B138" t="s">
-        <v>296</v>
+        <v>93</v>
       </c>
       <c r="C138" t="s">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="D138">
-        <v>2017</v>
+        <v>2004</v>
       </c>
       <c r="E138" t="s">
         <v>26</v>
@@ -10269,36 +10269,36 @@
         <v>73</v>
       </c>
       <c r="G138" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="H138" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="I138" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="J138" t="s">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c r="K138" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="L138" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="B139" t="s">
-        <v>306</v>
+        <v>94</v>
       </c>
       <c r="C139" t="s">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="D139">
-        <v>2017</v>
+        <v>2005</v>
       </c>
       <c r="E139" t="s">
         <v>26</v>
@@ -10307,16 +10307,16 @@
         <v>73</v>
       </c>
       <c r="G139" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H139" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I139" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J139" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K139" t="s">
         <v>115</v>
@@ -10327,16 +10327,16 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="8" t="s">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="B140" t="s">
-        <v>313</v>
+        <v>95</v>
       </c>
       <c r="C140" t="s">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="D140">
-        <v>2017</v>
+        <v>2006</v>
       </c>
       <c r="E140" t="s">
         <v>26</v>
@@ -10345,36 +10345,36 @@
         <v>73</v>
       </c>
       <c r="G140" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H140" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I140" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J140" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K140" t="s">
+        <v>47</v>
+      </c>
+      <c r="L140" t="s">
         <v>115</v>
-      </c>
-      <c r="L140" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="B141" t="s">
-        <v>327</v>
+        <v>96</v>
       </c>
       <c r="C141" t="s">
-        <v>320</v>
+        <v>83</v>
       </c>
       <c r="D141">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="E141" t="s">
         <v>26</v>
@@ -10383,19 +10383,19 @@
         <v>73</v>
       </c>
       <c r="G141" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H141" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I141" t="s">
         <v>29</v>
       </c>
       <c r="J141" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="K141" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L141" t="s">
         <v>47</v>
@@ -10403,16 +10403,16 @@
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="B142" t="s">
-        <v>332</v>
+        <v>97</v>
       </c>
       <c r="C142" t="s">
-        <v>321</v>
+        <v>83</v>
       </c>
       <c r="D142">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="E142" t="s">
         <v>26</v>
@@ -10421,36 +10421,36 @@
         <v>73</v>
       </c>
       <c r="G142" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H142" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I142" t="s">
         <v>29</v>
       </c>
       <c r="J142" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="K142" t="s">
-        <v>339</v>
+        <v>115</v>
       </c>
       <c r="L142" t="s">
-        <v>338</v>
+        <v>47</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="8" t="s">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="B143" t="s">
-        <v>307</v>
+        <v>98</v>
       </c>
       <c r="C143" t="s">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="D143">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="E143" t="s">
         <v>26</v>
@@ -10459,16 +10459,16 @@
         <v>73</v>
       </c>
       <c r="G143" t="s">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="H143" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I143" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J143" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K143" t="s">
         <v>47</v>
@@ -10479,16 +10479,16 @@
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="8" t="s">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="B144" t="s">
-        <v>314</v>
+        <v>99</v>
       </c>
       <c r="C144" t="s">
-        <v>299</v>
+        <v>83</v>
       </c>
       <c r="D144">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="E144" t="s">
         <v>26</v>
@@ -10497,36 +10497,36 @@
         <v>73</v>
       </c>
       <c r="G144" t="s">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="H144" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I144" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J144" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K144" t="s">
         <v>47</v>
       </c>
       <c r="L144" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="8" t="s">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="B145" t="s">
-        <v>328</v>
+        <v>100</v>
       </c>
       <c r="C145" t="s">
-        <v>320</v>
+        <v>84</v>
       </c>
       <c r="D145">
-        <v>2018</v>
+        <v>2004</v>
       </c>
       <c r="E145" t="s">
         <v>26</v>
@@ -10535,36 +10535,36 @@
         <v>73</v>
       </c>
       <c r="G145" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H145" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I145" t="s">
         <v>29</v>
       </c>
       <c r="J145" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="K145" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L145" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="B146" t="s">
-        <v>333</v>
+        <v>101</v>
       </c>
       <c r="C146" t="s">
-        <v>321</v>
+        <v>84</v>
       </c>
       <c r="D146">
-        <v>2018</v>
+        <v>2005</v>
       </c>
       <c r="E146" t="s">
         <v>26</v>
@@ -10573,150 +10573,150 @@
         <v>73</v>
       </c>
       <c r="G146" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H146" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I146" t="s">
         <v>29</v>
       </c>
       <c r="J146" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="K146" t="s">
+        <v>115</v>
+      </c>
+      <c r="L146" t="s">
         <v>47</v>
-      </c>
-      <c r="L146" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="8" t="s">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="B147" t="s">
-        <v>352</v>
+        <v>102</v>
       </c>
       <c r="C147" t="s">
-        <v>341</v>
+        <v>84</v>
       </c>
       <c r="D147">
-        <v>2018</v>
+        <v>2006</v>
       </c>
       <c r="E147" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F147" t="s">
         <v>73</v>
       </c>
       <c r="G147" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H147" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I147" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J147" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K147" t="s">
-        <v>361</v>
+        <v>47</v>
       </c>
       <c r="L147" t="s">
-        <v>363</v>
+        <v>115</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="8" t="s">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="B148" t="s">
-        <v>353</v>
+        <v>103</v>
       </c>
       <c r="C148" t="s">
-        <v>340</v>
+        <v>84</v>
       </c>
       <c r="D148">
-        <v>2018</v>
+        <v>2007</v>
       </c>
       <c r="E148" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F148" t="s">
         <v>73</v>
       </c>
       <c r="G148" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H148" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I148" t="s">
         <v>29</v>
       </c>
       <c r="J148" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K148" t="s">
         <v>47</v>
       </c>
       <c r="L148" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A149" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B149" t="s">
+        <v>104</v>
+      </c>
+      <c r="C149" t="s">
+        <v>84</v>
+      </c>
+      <c r="D149">
+        <v>2008</v>
+      </c>
+      <c r="E149" t="s">
+        <v>26</v>
+      </c>
+      <c r="F149" t="s">
+        <v>73</v>
+      </c>
+      <c r="G149" t="s">
+        <v>114</v>
+      </c>
+      <c r="H149" t="s">
+        <v>29</v>
+      </c>
+      <c r="I149" t="s">
+        <v>29</v>
+      </c>
+      <c r="J149" t="s">
+        <v>176</v>
+      </c>
+      <c r="K149" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>344</v>
-      </c>
-      <c r="B149" t="s">
-        <v>356</v>
-      </c>
-      <c r="C149" t="s">
-        <v>342</v>
-      </c>
-      <c r="D149">
-        <v>2018</v>
-      </c>
-      <c r="E149" t="s">
-        <v>15</v>
-      </c>
-      <c r="F149" t="s">
-        <v>73</v>
-      </c>
-      <c r="G149" t="s">
-        <v>263</v>
-      </c>
-      <c r="H149" t="s">
-        <v>90</v>
-      </c>
-      <c r="I149" t="s">
-        <v>90</v>
-      </c>
-      <c r="J149" t="s">
-        <v>90</v>
-      </c>
-      <c r="K149" t="s">
-        <v>45</v>
-      </c>
       <c r="L149" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="18" t="s">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="B150" t="s">
-        <v>308</v>
+        <v>105</v>
       </c>
       <c r="C150" t="s">
-        <v>298</v>
+        <v>84</v>
       </c>
       <c r="D150">
-        <v>2019</v>
+        <v>2009</v>
       </c>
       <c r="E150" t="s">
         <v>26</v>
@@ -10725,36 +10725,36 @@
         <v>73</v>
       </c>
       <c r="G150" t="s">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="H150" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I150" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J150" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K150" t="s">
         <v>47</v>
       </c>
       <c r="L150" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="18" t="s">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="B151" t="s">
-        <v>315</v>
+        <v>106</v>
       </c>
       <c r="C151" t="s">
-        <v>299</v>
+        <v>84</v>
       </c>
       <c r="D151">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="E151" t="s">
         <v>26</v>
@@ -10763,16 +10763,16 @@
         <v>73</v>
       </c>
       <c r="G151" t="s">
-        <v>263</v>
+        <v>114</v>
       </c>
       <c r="H151" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I151" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J151" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K151" t="s">
         <v>47</v>
@@ -10783,16 +10783,16 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="B152" t="s">
-        <v>329</v>
+        <v>107</v>
       </c>
       <c r="C152" t="s">
-        <v>320</v>
+        <v>85</v>
       </c>
       <c r="D152">
-        <v>2019</v>
+        <v>2004</v>
       </c>
       <c r="E152" t="s">
         <v>26</v>
@@ -10801,36 +10801,36 @@
         <v>73</v>
       </c>
       <c r="G152" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H152" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I152" t="s">
         <v>29</v>
       </c>
       <c r="J152" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="K152" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="L152" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="B153" t="s">
-        <v>334</v>
+        <v>108</v>
       </c>
       <c r="C153" t="s">
-        <v>321</v>
+        <v>85</v>
       </c>
       <c r="D153">
-        <v>2019</v>
+        <v>2005</v>
       </c>
       <c r="E153" t="s">
         <v>26</v>
@@ -10839,92 +10839,92 @@
         <v>73</v>
       </c>
       <c r="G153" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H153" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I153" t="s">
         <v>29</v>
       </c>
       <c r="J153" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="K153" t="s">
         <v>47</v>
       </c>
       <c r="L153" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="B154" t="s">
-        <v>359</v>
+        <v>109</v>
       </c>
       <c r="C154" t="s">
-        <v>341</v>
+        <v>85</v>
       </c>
       <c r="D154">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="E154" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F154" t="s">
         <v>73</v>
       </c>
       <c r="G154" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H154" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I154" t="s">
         <v>29</v>
       </c>
       <c r="J154" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K154" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L154" t="s">
-        <v>361</v>
+        <v>47</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>344</v>
+        <v>82</v>
       </c>
       <c r="B155" t="s">
-        <v>354</v>
+        <v>110</v>
       </c>
       <c r="C155" t="s">
-        <v>340</v>
+        <v>85</v>
       </c>
       <c r="D155">
-        <v>2019</v>
+        <v>2007</v>
       </c>
       <c r="E155" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F155" t="s">
         <v>73</v>
       </c>
       <c r="G155" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H155" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I155" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J155" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K155" t="s">
         <v>115</v>
@@ -10934,55 +10934,55 @@
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>344</v>
+      <c r="A156" s="18" t="s">
+        <v>82</v>
       </c>
       <c r="B156" t="s">
-        <v>357</v>
+        <v>111</v>
       </c>
       <c r="C156" t="s">
-        <v>342</v>
+        <v>85</v>
       </c>
       <c r="D156">
-        <v>2019</v>
+        <v>2008</v>
       </c>
       <c r="E156" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F156" t="s">
         <v>73</v>
       </c>
       <c r="G156" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="H156" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I156" t="s">
         <v>29</v>
       </c>
       <c r="J156" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K156" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L156" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
-        <v>364</v>
+      <c r="A157" s="18" t="s">
+        <v>82</v>
       </c>
       <c r="B157" t="s">
-        <v>372</v>
+        <v>112</v>
       </c>
       <c r="C157" t="s">
-        <v>365</v>
+        <v>85</v>
       </c>
       <c r="D157">
-        <v>2019</v>
+        <v>2009</v>
       </c>
       <c r="E157" t="s">
         <v>26</v>
@@ -10991,36 +10991,36 @@
         <v>73</v>
       </c>
       <c r="G157" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H157" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I157" t="s">
         <v>29</v>
       </c>
       <c r="J157" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K157" t="s">
-        <v>382</v>
+        <v>47</v>
       </c>
       <c r="L157" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>364</v>
+      <c r="A158" s="18" t="s">
+        <v>82</v>
       </c>
       <c r="B158" t="s">
-        <v>381</v>
+        <v>113</v>
       </c>
       <c r="C158" t="s">
-        <v>366</v>
+        <v>85</v>
       </c>
       <c r="D158">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="E158" t="s">
         <v>26</v>
@@ -11029,36 +11029,36 @@
         <v>73</v>
       </c>
       <c r="G158" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="H158" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I158" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J158" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="K158" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="L158" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>414</v>
+      <c r="A159" s="18" t="s">
+        <v>318</v>
       </c>
       <c r="B159" t="s">
-        <v>390</v>
+        <v>304</v>
       </c>
       <c r="C159" t="s">
-        <v>384</v>
+        <v>298</v>
       </c>
       <c r="D159">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="E159" t="s">
         <v>26</v>
@@ -11067,10 +11067,10 @@
         <v>73</v>
       </c>
       <c r="G159" t="s">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="H159" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I159" t="s">
         <v>90</v>
@@ -11079,24 +11079,24 @@
         <v>90</v>
       </c>
       <c r="K159" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L159" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
-        <v>415</v>
+      <c r="A160" s="18" t="s">
+        <v>318</v>
       </c>
       <c r="B160" t="s">
-        <v>392</v>
+        <v>305</v>
       </c>
       <c r="C160" t="s">
-        <v>385</v>
+        <v>298</v>
       </c>
       <c r="D160">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="E160" t="s">
         <v>26</v>
@@ -11105,46 +11105,46 @@
         <v>73</v>
       </c>
       <c r="G160" t="s">
+        <v>263</v>
+      </c>
+      <c r="H160" t="s">
+        <v>90</v>
+      </c>
+      <c r="I160" t="s">
+        <v>90</v>
+      </c>
+      <c r="J160" t="s">
+        <v>90</v>
+      </c>
+      <c r="K160" t="s">
+        <v>47</v>
+      </c>
+      <c r="L160" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A161" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="B161" t="s">
+        <v>306</v>
+      </c>
+      <c r="C161" t="s">
+        <v>298</v>
+      </c>
+      <c r="D161">
+        <v>2017</v>
+      </c>
+      <c r="E161" t="s">
+        <v>26</v>
+      </c>
+      <c r="F161" t="s">
+        <v>73</v>
+      </c>
+      <c r="G161" t="s">
         <v>79</v>
       </c>
-      <c r="H160" t="s">
-        <v>29</v>
-      </c>
-      <c r="I160" t="s">
-        <v>29</v>
-      </c>
-      <c r="J160" t="s">
-        <v>90</v>
-      </c>
-      <c r="K160" t="s">
-        <v>81</v>
-      </c>
-      <c r="L160" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>413</v>
-      </c>
-      <c r="B161" t="s">
-        <v>418</v>
-      </c>
-      <c r="C161" t="s">
-        <v>400</v>
-      </c>
-      <c r="D161">
-        <v>2019</v>
-      </c>
-      <c r="E161" t="s">
-        <v>26</v>
-      </c>
-      <c r="F161" t="s">
-        <v>73</v>
-      </c>
-      <c r="G161" t="s">
-        <v>80</v>
-      </c>
       <c r="H161" t="s">
         <v>90</v>
       </c>
@@ -11152,27 +11152,27 @@
         <v>90</v>
       </c>
       <c r="J161" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K161" t="s">
-        <v>408</v>
+        <v>115</v>
       </c>
       <c r="L161" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
-        <v>416</v>
+      <c r="A162" s="18" t="s">
+        <v>318</v>
       </c>
       <c r="B162" t="s">
-        <v>424</v>
+        <v>307</v>
       </c>
       <c r="C162" t="s">
-        <v>401</v>
+        <v>298</v>
       </c>
       <c r="D162">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="E162" t="s">
         <v>26</v>
@@ -11190,27 +11190,27 @@
         <v>90</v>
       </c>
       <c r="J162" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K162" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L162" t="s">
-        <v>429</v>
+        <v>115</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A163" s="18" t="s">
+      <c r="A163" t="s">
         <v>318</v>
       </c>
       <c r="B163" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C163" t="s">
         <v>298</v>
       </c>
       <c r="D163">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E163" t="s">
         <v>26</v>
@@ -11219,7 +11219,7 @@
         <v>73</v>
       </c>
       <c r="G163" t="s">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="H163" t="s">
         <v>90</v>
@@ -11231,21 +11231,21 @@
         <v>90</v>
       </c>
       <c r="K163" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="L163" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A164" s="18" t="s">
+      <c r="A164" t="s">
         <v>318</v>
       </c>
       <c r="B164" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C164" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D164">
         <v>2020</v>
@@ -11277,16 +11277,16 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B165" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="C165" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="D165">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E165" t="s">
         <v>26</v>
@@ -11295,83 +11295,83 @@
         <v>73</v>
       </c>
       <c r="G165" t="s">
+        <v>263</v>
+      </c>
+      <c r="H165" t="s">
+        <v>90</v>
+      </c>
+      <c r="I165" t="s">
+        <v>90</v>
+      </c>
+      <c r="J165" t="s">
+        <v>90</v>
+      </c>
+      <c r="K165" t="s">
+        <v>47</v>
+      </c>
+      <c r="L165" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A166" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="B166" t="s">
+        <v>311</v>
+      </c>
+      <c r="C166" t="s">
+        <v>299</v>
+      </c>
+      <c r="D166">
+        <v>2015</v>
+      </c>
+      <c r="E166" t="s">
+        <v>26</v>
+      </c>
+      <c r="F166" t="s">
+        <v>73</v>
+      </c>
+      <c r="G166" t="s">
         <v>79</v>
       </c>
-      <c r="H165" t="s">
-        <v>90</v>
-      </c>
-      <c r="I165" t="s">
-        <v>29</v>
-      </c>
-      <c r="J165" t="s">
-        <v>29</v>
-      </c>
-      <c r="K165" t="s">
-        <v>45</v>
-      </c>
-      <c r="L165" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
-        <v>319</v>
-      </c>
-      <c r="B166" t="s">
-        <v>335</v>
-      </c>
-      <c r="C166" t="s">
-        <v>321</v>
-      </c>
-      <c r="D166">
-        <v>2020</v>
-      </c>
-      <c r="E166" t="s">
-        <v>26</v>
-      </c>
-      <c r="F166" t="s">
-        <v>73</v>
-      </c>
-      <c r="G166" t="s">
-        <v>80</v>
-      </c>
       <c r="H166" t="s">
         <v>90</v>
       </c>
       <c r="I166" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J166" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K166" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="L166" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>344</v>
+      <c r="A167" s="18" t="s">
+        <v>318</v>
       </c>
       <c r="B167" t="s">
-        <v>360</v>
+        <v>312</v>
       </c>
       <c r="C167" t="s">
-        <v>341</v>
+        <v>299</v>
       </c>
       <c r="D167">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="E167" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F167" t="s">
         <v>73</v>
       </c>
       <c r="G167" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="H167" t="s">
         <v>90</v>
@@ -11383,100 +11383,100 @@
         <v>90</v>
       </c>
       <c r="K167" t="s">
-        <v>362</v>
+        <v>47</v>
       </c>
       <c r="L167" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>344</v>
+      <c r="A168" s="18" t="s">
+        <v>318</v>
       </c>
       <c r="B168" t="s">
-        <v>355</v>
+        <v>313</v>
       </c>
       <c r="C168" t="s">
-        <v>340</v>
+        <v>299</v>
       </c>
       <c r="D168">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="E168" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F168" t="s">
         <v>73</v>
       </c>
       <c r="G168" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H168" t="s">
         <v>90</v>
       </c>
       <c r="I168" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J168" t="s">
         <v>90</v>
       </c>
       <c r="K168" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="L168" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A169" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="B169" t="s">
+        <v>314</v>
+      </c>
+      <c r="C169" t="s">
+        <v>299</v>
+      </c>
+      <c r="D169">
+        <v>2018</v>
+      </c>
+      <c r="E169" t="s">
+        <v>26</v>
+      </c>
+      <c r="F169" t="s">
+        <v>73</v>
+      </c>
+      <c r="G169" t="s">
+        <v>263</v>
+      </c>
+      <c r="H169" t="s">
+        <v>90</v>
+      </c>
+      <c r="I169" t="s">
+        <v>90</v>
+      </c>
+      <c r="J169" t="s">
+        <v>90</v>
+      </c>
+      <c r="K169" t="s">
+        <v>47</v>
+      </c>
+      <c r="L169" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>344</v>
-      </c>
-      <c r="B169" t="s">
-        <v>358</v>
-      </c>
-      <c r="C169" t="s">
-        <v>342</v>
-      </c>
-      <c r="D169">
-        <v>2020</v>
-      </c>
-      <c r="E169" t="s">
-        <v>15</v>
-      </c>
-      <c r="F169" t="s">
-        <v>73</v>
-      </c>
-      <c r="G169" t="s">
-        <v>79</v>
-      </c>
-      <c r="H169" t="s">
-        <v>90</v>
-      </c>
-      <c r="I169" t="s">
-        <v>29</v>
-      </c>
-      <c r="J169" t="s">
-        <v>90</v>
-      </c>
-      <c r="K169" t="s">
-        <v>45</v>
-      </c>
-      <c r="L169" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="B170" t="s">
-        <v>377</v>
+        <v>315</v>
       </c>
       <c r="C170" t="s">
-        <v>365</v>
+        <v>299</v>
       </c>
       <c r="D170">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E170" t="s">
         <v>26</v>
@@ -11497,21 +11497,21 @@
         <v>90</v>
       </c>
       <c r="K170" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L170" t="s">
-        <v>382</v>
+        <v>47</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>364</v>
+        <v>318</v>
       </c>
       <c r="B171" t="s">
-        <v>373</v>
+        <v>316</v>
       </c>
       <c r="C171" t="s">
-        <v>366</v>
+        <v>299</v>
       </c>
       <c r="D171">
         <v>2020</v>
@@ -11523,7 +11523,7 @@
         <v>73</v>
       </c>
       <c r="G171" t="s">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="H171" t="s">
         <v>90</v>
@@ -11535,7 +11535,7 @@
         <v>90</v>
       </c>
       <c r="K171" t="s">
-        <v>383</v>
+        <v>115</v>
       </c>
       <c r="L171" t="s">
         <v>47</v>
@@ -11543,16 +11543,16 @@
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>414</v>
+        <v>318</v>
       </c>
       <c r="B172" t="s">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="C172" t="s">
-        <v>384</v>
+        <v>299</v>
       </c>
       <c r="D172">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E172" t="s">
         <v>26</v>
@@ -11561,10 +11561,10 @@
         <v>73</v>
       </c>
       <c r="G172" t="s">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="H172" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I172" t="s">
         <v>90</v>
@@ -11573,24 +11573,24 @@
         <v>90</v>
       </c>
       <c r="K172" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L172" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>415</v>
+        <v>364</v>
       </c>
       <c r="B173" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="C173" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="D173">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="E173" t="s">
         <v>26</v>
@@ -11602,7 +11602,7 @@
         <v>80</v>
       </c>
       <c r="H173" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I173" t="s">
         <v>29</v>
@@ -11611,21 +11611,21 @@
         <v>90</v>
       </c>
       <c r="K173" t="s">
-        <v>115</v>
+        <v>382</v>
       </c>
       <c r="L173" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>413</v>
+        <v>364</v>
       </c>
       <c r="B174" t="s">
-        <v>419</v>
+        <v>377</v>
       </c>
       <c r="C174" t="s">
-        <v>400</v>
+        <v>365</v>
       </c>
       <c r="D174">
         <v>2020</v>
@@ -11646,27 +11646,27 @@
         <v>90</v>
       </c>
       <c r="J174" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K174" t="s">
-        <v>423</v>
+        <v>45</v>
       </c>
       <c r="L174" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>416</v>
+        <v>364</v>
       </c>
       <c r="B175" t="s">
-        <v>425</v>
+        <v>378</v>
       </c>
       <c r="C175" t="s">
-        <v>401</v>
+        <v>365</v>
       </c>
       <c r="D175">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E175" t="s">
         <v>26</v>
@@ -11684,7 +11684,7 @@
         <v>90</v>
       </c>
       <c r="J175" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K175" t="s">
         <v>45</v>
@@ -11694,17 +11694,17 @@
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A176" s="18" t="s">
-        <v>318</v>
+      <c r="A176" t="s">
+        <v>364</v>
       </c>
       <c r="B176" t="s">
-        <v>310</v>
+        <v>379</v>
       </c>
       <c r="C176" t="s">
-        <v>298</v>
+        <v>365</v>
       </c>
       <c r="D176">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E176" t="s">
         <v>26</v>
@@ -11713,7 +11713,7 @@
         <v>73</v>
       </c>
       <c r="G176" t="s">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="H176" t="s">
         <v>90</v>
@@ -11725,24 +11725,24 @@
         <v>90</v>
       </c>
       <c r="K176" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L176" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A177" s="18" t="s">
-        <v>318</v>
+      <c r="A177" t="s">
+        <v>364</v>
       </c>
       <c r="B177" t="s">
-        <v>317</v>
+        <v>380</v>
       </c>
       <c r="C177" t="s">
-        <v>299</v>
+        <v>365</v>
       </c>
       <c r="D177">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E177" t="s">
         <v>26</v>
@@ -11751,7 +11751,7 @@
         <v>73</v>
       </c>
       <c r="G177" t="s">
-        <v>263</v>
+        <v>79</v>
       </c>
       <c r="H177" t="s">
         <v>90</v>
@@ -11763,24 +11763,24 @@
         <v>90</v>
       </c>
       <c r="K177" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L177" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="B178" t="s">
-        <v>331</v>
+        <v>381</v>
       </c>
       <c r="C178" t="s">
-        <v>320</v>
+        <v>366</v>
       </c>
       <c r="D178">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="E178" t="s">
         <v>26</v>
@@ -11795,30 +11795,30 @@
         <v>90</v>
       </c>
       <c r="I178" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J178" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K178" t="s">
         <v>47</v>
       </c>
       <c r="L178" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>319</v>
+        <v>364</v>
       </c>
       <c r="B179" t="s">
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="C179" t="s">
-        <v>321</v>
+        <v>366</v>
       </c>
       <c r="D179">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E179" t="s">
         <v>26</v>
@@ -11827,19 +11827,19 @@
         <v>73</v>
       </c>
       <c r="G179" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="H179" t="s">
         <v>90</v>
       </c>
       <c r="I179" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J179" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K179" t="s">
-        <v>47</v>
+        <v>383</v>
       </c>
       <c r="L179" t="s">
         <v>47</v>
@@ -11850,10 +11850,10 @@
         <v>364</v>
       </c>
       <c r="B180" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C180" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D180">
         <v>2021</v>
@@ -11877,10 +11877,10 @@
         <v>90</v>
       </c>
       <c r="K180" t="s">
-        <v>45</v>
+        <v>383</v>
       </c>
       <c r="L180" t="s">
-        <v>45</v>
+        <v>383</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
@@ -11888,13 +11888,13 @@
         <v>364</v>
       </c>
       <c r="B181" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C181" t="s">
         <v>366</v>
       </c>
       <c r="D181">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E181" t="s">
         <v>26</v>
@@ -11915,7 +11915,7 @@
         <v>90</v>
       </c>
       <c r="K181" t="s">
-        <v>383</v>
+        <v>115</v>
       </c>
       <c r="L181" t="s">
         <v>383</v>
@@ -11923,16 +11923,16 @@
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>414</v>
+        <v>364</v>
       </c>
       <c r="B182" t="s">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="C182" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="D182">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E182" t="s">
         <v>26</v>
@@ -11941,77 +11941,77 @@
         <v>73</v>
       </c>
       <c r="G182" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="H182" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I182" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J182" t="s">
         <v>90</v>
       </c>
       <c r="K182" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L182" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>415</v>
+        <v>344</v>
       </c>
       <c r="B183" t="s">
-        <v>394</v>
+        <v>356</v>
       </c>
       <c r="C183" t="s">
-        <v>385</v>
+        <v>342</v>
       </c>
       <c r="D183">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="E183" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F183" t="s">
         <v>73</v>
       </c>
       <c r="G183" t="s">
-        <v>79</v>
+        <v>263</v>
       </c>
       <c r="H183" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I183" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="J183" t="s">
         <v>90</v>
       </c>
       <c r="K183" t="s">
+        <v>45</v>
+      </c>
+      <c r="L183" t="s">
         <v>81</v>
-      </c>
-      <c r="L183" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>413</v>
+        <v>344</v>
       </c>
       <c r="B184" t="s">
-        <v>420</v>
+        <v>357</v>
       </c>
       <c r="C184" t="s">
-        <v>400</v>
+        <v>342</v>
       </c>
       <c r="D184">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="E184" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F184" t="s">
         <v>73</v>
@@ -12023,68 +12023,68 @@
         <v>90</v>
       </c>
       <c r="I184" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J184" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K184" t="s">
-        <v>423</v>
+        <v>45</v>
       </c>
       <c r="L184" t="s">
-        <v>423</v>
+        <v>45</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>416</v>
+        <v>344</v>
       </c>
       <c r="B185" t="s">
-        <v>426</v>
+        <v>358</v>
       </c>
       <c r="C185" t="s">
-        <v>401</v>
+        <v>342</v>
       </c>
       <c r="D185">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E185" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F185" t="s">
         <v>73</v>
       </c>
       <c r="G185" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H185" t="s">
         <v>90</v>
       </c>
       <c r="I185" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J185" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="K185" t="s">
-        <v>408</v>
+        <v>45</v>
       </c>
       <c r="L185" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
-        <v>417</v>
+      <c r="A186" s="18" t="s">
+        <v>264</v>
       </c>
       <c r="B186" t="s">
-        <v>430</v>
+        <v>276</v>
       </c>
       <c r="C186" t="s">
-        <v>402</v>
+        <v>277</v>
       </c>
       <c r="D186">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="E186" t="s">
         <v>26</v>
@@ -12099,30 +12099,30 @@
         <v>90</v>
       </c>
       <c r="I186" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J186" t="s">
         <v>29</v>
       </c>
       <c r="K186" t="s">
-        <v>408</v>
+        <v>47</v>
       </c>
       <c r="L186" t="s">
-        <v>433</v>
+        <v>47</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
-        <v>364</v>
+      <c r="A187" s="18" t="s">
+        <v>264</v>
       </c>
       <c r="B187" t="s">
-        <v>379</v>
+        <v>278</v>
       </c>
       <c r="C187" t="s">
-        <v>365</v>
+        <v>277</v>
       </c>
       <c r="D187">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="E187" t="s">
         <v>26</v>
@@ -12131,226 +12131,226 @@
         <v>73</v>
       </c>
       <c r="G187" t="s">
+        <v>80</v>
+      </c>
+      <c r="H187" t="s">
+        <v>90</v>
+      </c>
+      <c r="I187" t="s">
+        <v>29</v>
+      </c>
+      <c r="J187" t="s">
+        <v>29</v>
+      </c>
+      <c r="K187" t="s">
+        <v>47</v>
+      </c>
+      <c r="L187" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A188" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B188" t="s">
+        <v>279</v>
+      </c>
+      <c r="C188" t="s">
+        <v>277</v>
+      </c>
+      <c r="D188">
+        <v>2013</v>
+      </c>
+      <c r="E188" t="s">
+        <v>26</v>
+      </c>
+      <c r="F188" t="s">
+        <v>73</v>
+      </c>
+      <c r="G188" t="s">
+        <v>80</v>
+      </c>
+      <c r="H188" t="s">
+        <v>90</v>
+      </c>
+      <c r="I188" t="s">
+        <v>29</v>
+      </c>
+      <c r="J188" t="s">
+        <v>29</v>
+      </c>
+      <c r="K188" t="s">
+        <v>47</v>
+      </c>
+      <c r="L188" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A189" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B189" t="s">
+        <v>280</v>
+      </c>
+      <c r="C189" t="s">
+        <v>277</v>
+      </c>
+      <c r="D189">
+        <v>2014</v>
+      </c>
+      <c r="E189" t="s">
+        <v>26</v>
+      </c>
+      <c r="F189" t="s">
+        <v>73</v>
+      </c>
+      <c r="G189" t="s">
+        <v>263</v>
+      </c>
+      <c r="H189" t="s">
+        <v>90</v>
+      </c>
+      <c r="I189" t="s">
+        <v>29</v>
+      </c>
+      <c r="J189" t="s">
+        <v>29</v>
+      </c>
+      <c r="K189" t="s">
+        <v>115</v>
+      </c>
+      <c r="L189" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A190" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B190" t="s">
+        <v>281</v>
+      </c>
+      <c r="C190" t="s">
+        <v>277</v>
+      </c>
+      <c r="D190">
+        <v>2015</v>
+      </c>
+      <c r="E190" t="s">
+        <v>26</v>
+      </c>
+      <c r="F190" t="s">
+        <v>73</v>
+      </c>
+      <c r="G190" t="s">
+        <v>80</v>
+      </c>
+      <c r="H190" t="s">
+        <v>90</v>
+      </c>
+      <c r="I190" t="s">
+        <v>29</v>
+      </c>
+      <c r="J190" t="s">
+        <v>29</v>
+      </c>
+      <c r="K190" t="s">
+        <v>47</v>
+      </c>
+      <c r="L190" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A191" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B191" t="s">
+        <v>282</v>
+      </c>
+      <c r="C191" t="s">
+        <v>277</v>
+      </c>
+      <c r="D191">
+        <v>2016</v>
+      </c>
+      <c r="E191" t="s">
+        <v>26</v>
+      </c>
+      <c r="F191" t="s">
+        <v>73</v>
+      </c>
+      <c r="G191" t="s">
+        <v>80</v>
+      </c>
+      <c r="H191" t="s">
+        <v>90</v>
+      </c>
+      <c r="I191" t="s">
+        <v>29</v>
+      </c>
+      <c r="J191" t="s">
+        <v>29</v>
+      </c>
+      <c r="K191" t="s">
+        <v>47</v>
+      </c>
+      <c r="L191" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A192" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B192" t="s">
+        <v>294</v>
+      </c>
+      <c r="C192" t="s">
+        <v>277</v>
+      </c>
+      <c r="D192">
+        <v>2017</v>
+      </c>
+      <c r="E192" t="s">
+        <v>26</v>
+      </c>
+      <c r="F192" t="s">
+        <v>73</v>
+      </c>
+      <c r="G192" t="s">
         <v>79</v>
       </c>
-      <c r="H187" t="s">
-        <v>90</v>
-      </c>
-      <c r="I187" t="s">
-        <v>90</v>
-      </c>
-      <c r="J187" t="s">
-        <v>90</v>
-      </c>
-      <c r="K187" t="s">
-        <v>45</v>
-      </c>
-      <c r="L187" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A188" t="s">
-        <v>364</v>
-      </c>
-      <c r="B188" t="s">
-        <v>375</v>
-      </c>
-      <c r="C188" t="s">
-        <v>366</v>
-      </c>
-      <c r="D188">
-        <v>2022</v>
-      </c>
-      <c r="E188" t="s">
-        <v>26</v>
-      </c>
-      <c r="F188" t="s">
-        <v>73</v>
-      </c>
-      <c r="G188" t="s">
-        <v>79</v>
-      </c>
-      <c r="H188" t="s">
-        <v>90</v>
-      </c>
-      <c r="I188" t="s">
-        <v>90</v>
-      </c>
-      <c r="J188" t="s">
-        <v>90</v>
-      </c>
-      <c r="K188" t="s">
-        <v>115</v>
-      </c>
-      <c r="L188" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A189" t="s">
-        <v>414</v>
-      </c>
-      <c r="B189" t="s">
-        <v>398</v>
-      </c>
-      <c r="C189" t="s">
-        <v>384</v>
-      </c>
-      <c r="D189">
-        <v>2022</v>
-      </c>
-      <c r="E189" t="s">
-        <v>26</v>
-      </c>
-      <c r="F189" t="s">
-        <v>73</v>
-      </c>
-      <c r="G189" t="s">
-        <v>114</v>
-      </c>
-      <c r="H189" t="s">
-        <v>29</v>
-      </c>
-      <c r="I189" t="s">
-        <v>29</v>
-      </c>
-      <c r="J189" t="s">
-        <v>90</v>
-      </c>
-      <c r="K189" t="s">
-        <v>81</v>
-      </c>
-      <c r="L189" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A190" t="s">
-        <v>415</v>
-      </c>
-      <c r="B190" t="s">
-        <v>395</v>
-      </c>
-      <c r="C190" t="s">
-        <v>385</v>
-      </c>
-      <c r="D190">
-        <v>2022</v>
-      </c>
-      <c r="E190" t="s">
-        <v>26</v>
-      </c>
-      <c r="F190" t="s">
-        <v>73</v>
-      </c>
-      <c r="G190" t="s">
-        <v>79</v>
-      </c>
-      <c r="H190" t="s">
-        <v>29</v>
-      </c>
-      <c r="I190" t="s">
-        <v>29</v>
-      </c>
-      <c r="J190" t="s">
-        <v>90</v>
-      </c>
-      <c r="K190" t="s">
-        <v>81</v>
-      </c>
-      <c r="L190" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A191" t="s">
-        <v>413</v>
-      </c>
-      <c r="B191" t="s">
-        <v>421</v>
-      </c>
-      <c r="C191" t="s">
-        <v>400</v>
-      </c>
-      <c r="D191">
-        <v>2022</v>
-      </c>
-      <c r="E191" t="s">
-        <v>26</v>
-      </c>
-      <c r="F191" t="s">
-        <v>73</v>
-      </c>
-      <c r="G191" t="s">
-        <v>79</v>
-      </c>
-      <c r="H191" t="s">
-        <v>90</v>
-      </c>
-      <c r="I191" t="s">
-        <v>90</v>
-      </c>
-      <c r="J191" t="s">
-        <v>29</v>
-      </c>
-      <c r="K191" t="s">
-        <v>423</v>
-      </c>
-      <c r="L191" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A192" t="s">
-        <v>416</v>
-      </c>
-      <c r="B192" t="s">
-        <v>427</v>
-      </c>
-      <c r="C192" t="s">
-        <v>401</v>
-      </c>
-      <c r="D192">
-        <v>2022</v>
-      </c>
-      <c r="E192" t="s">
-        <v>26</v>
-      </c>
-      <c r="F192" t="s">
-        <v>73</v>
-      </c>
-      <c r="G192" t="s">
-        <v>80</v>
-      </c>
       <c r="H192" t="s">
         <v>90</v>
       </c>
       <c r="I192" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J192" t="s">
         <v>29</v>
       </c>
       <c r="K192" t="s">
-        <v>429</v>
+        <v>47</v>
       </c>
       <c r="L192" t="s">
-        <v>408</v>
+        <v>47</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A193" t="s">
-        <v>417</v>
+      <c r="A193" s="18" t="s">
+        <v>264</v>
       </c>
       <c r="B193" t="s">
-        <v>431</v>
+        <v>283</v>
       </c>
       <c r="C193" t="s">
-        <v>402</v>
+        <v>284</v>
       </c>
       <c r="D193">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="E193" t="s">
         <v>26</v>
@@ -12365,30 +12365,30 @@
         <v>90</v>
       </c>
       <c r="I193" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J193" t="s">
         <v>90</v>
       </c>
       <c r="K193" t="s">
-        <v>429</v>
+        <v>47</v>
       </c>
       <c r="L193" t="s">
-        <v>408</v>
+        <v>115</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
-        <v>434</v>
+      <c r="A194" s="18" t="s">
+        <v>264</v>
       </c>
       <c r="B194" t="s">
-        <v>447</v>
+        <v>285</v>
       </c>
       <c r="C194" t="s">
-        <v>437</v>
+        <v>284</v>
       </c>
       <c r="D194">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="E194" t="s">
         <v>26</v>
@@ -12397,48 +12397,48 @@
         <v>73</v>
       </c>
       <c r="G194" t="s">
+        <v>80</v>
+      </c>
+      <c r="H194" t="s">
+        <v>90</v>
+      </c>
+      <c r="I194" t="s">
+        <v>29</v>
+      </c>
+      <c r="J194" t="s">
+        <v>90</v>
+      </c>
+      <c r="K194" t="s">
+        <v>45</v>
+      </c>
+      <c r="L194" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A195" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="B195" t="s">
+        <v>286</v>
+      </c>
+      <c r="C195" t="s">
+        <v>284</v>
+      </c>
+      <c r="D195">
+        <v>2013</v>
+      </c>
+      <c r="E195" t="s">
+        <v>26</v>
+      </c>
+      <c r="F195" t="s">
+        <v>73</v>
+      </c>
+      <c r="G195" t="s">
         <v>79</v>
       </c>
-      <c r="H194" t="s">
-        <v>90</v>
-      </c>
-      <c r="I194" t="s">
-        <v>29</v>
-      </c>
-      <c r="J194" t="s">
-        <v>90</v>
-      </c>
-      <c r="K194" t="s">
-        <v>81</v>
-      </c>
-      <c r="L194" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A195" t="s">
-        <v>435</v>
-      </c>
-      <c r="B195" t="s">
-        <v>449</v>
-      </c>
-      <c r="C195" t="s">
-        <v>438</v>
-      </c>
-      <c r="D195">
-        <v>2022</v>
-      </c>
-      <c r="E195" t="s">
-        <v>26</v>
-      </c>
-      <c r="F195" t="s">
-        <v>73</v>
-      </c>
-      <c r="G195" t="s">
-        <v>114</v>
-      </c>
       <c r="H195" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I195" t="s">
         <v>29</v>
@@ -12447,24 +12447,24 @@
         <v>90</v>
       </c>
       <c r="K195" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="L195" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A196" t="s">
-        <v>364</v>
+      <c r="A196" s="18" t="s">
+        <v>264</v>
       </c>
       <c r="B196" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C196" t="s">
-        <v>365</v>
+        <v>284</v>
       </c>
       <c r="D196">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="E196" t="s">
         <v>26</v>
@@ -12479,7 +12479,7 @@
         <v>90</v>
       </c>
       <c r="I196" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J196" t="s">
         <v>90</v>
@@ -12492,17 +12492,17 @@
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
-        <v>364</v>
+      <c r="A197" s="18" t="s">
+        <v>264</v>
       </c>
       <c r="B197" t="s">
-        <v>376</v>
+        <v>288</v>
       </c>
       <c r="C197" t="s">
-        <v>366</v>
+        <v>284</v>
       </c>
       <c r="D197">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="E197" t="s">
         <v>26</v>
@@ -12511,13 +12511,13 @@
         <v>73</v>
       </c>
       <c r="G197" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H197" t="s">
         <v>90</v>
       </c>
       <c r="I197" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="J197" t="s">
         <v>90</v>
@@ -12526,21 +12526,21 @@
         <v>47</v>
       </c>
       <c r="L197" t="s">
-        <v>115</v>
+        <v>45</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
-        <v>414</v>
+      <c r="A198" s="18" t="s">
+        <v>264</v>
       </c>
       <c r="B198" t="s">
-        <v>399</v>
+        <v>289</v>
       </c>
       <c r="C198" t="s">
-        <v>384</v>
+        <v>284</v>
       </c>
       <c r="D198">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E198" t="s">
         <v>26</v>
@@ -12549,10 +12549,10 @@
         <v>73</v>
       </c>
       <c r="G198" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="H198" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I198" t="s">
         <v>29</v>
@@ -12561,24 +12561,24 @@
         <v>90</v>
       </c>
       <c r="K198" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L198" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
-        <v>415</v>
+      <c r="A199" s="18" t="s">
+        <v>264</v>
       </c>
       <c r="B199" t="s">
-        <v>396</v>
+        <v>295</v>
       </c>
       <c r="C199" t="s">
-        <v>385</v>
+        <v>284</v>
       </c>
       <c r="D199">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="E199" t="s">
         <v>26</v>
@@ -12587,10 +12587,10 @@
         <v>73</v>
       </c>
       <c r="G199" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H199" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="I199" t="s">
         <v>29</v>
@@ -12599,24 +12599,24 @@
         <v>90</v>
       </c>
       <c r="K199" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="L199" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
-        <v>413</v>
+      <c r="A200" s="18" t="s">
+        <v>264</v>
       </c>
       <c r="B200" t="s">
-        <v>422</v>
+        <v>290</v>
       </c>
       <c r="C200" t="s">
-        <v>400</v>
+        <v>291</v>
       </c>
       <c r="D200">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="E200" t="s">
         <v>26</v>
@@ -12625,36 +12625,36 @@
         <v>73</v>
       </c>
       <c r="G200" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H200" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I200" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="J200" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="K200" t="s">
-        <v>408</v>
+        <v>73</v>
       </c>
       <c r="L200" t="s">
-        <v>423</v>
+        <v>73</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
-        <v>416</v>
+      <c r="A201" s="18" t="s">
+        <v>264</v>
       </c>
       <c r="B201" t="s">
-        <v>428</v>
+        <v>292</v>
       </c>
       <c r="C201" t="s">
-        <v>401</v>
+        <v>291</v>
       </c>
       <c r="D201">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="E201" t="s">
         <v>26</v>
@@ -12663,36 +12663,36 @@
         <v>73</v>
       </c>
       <c r="G201" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="H201" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I201" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="J201" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="K201" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="L201" t="s">
-        <v>429</v>
+        <v>73</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A202" t="s">
-        <v>417</v>
+      <c r="A202" s="18" t="s">
+        <v>264</v>
       </c>
       <c r="B202" t="s">
-        <v>432</v>
+        <v>293</v>
       </c>
       <c r="C202" t="s">
-        <v>402</v>
+        <v>291</v>
       </c>
       <c r="D202">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E202" t="s">
         <v>26</v>
@@ -12701,36 +12701,36 @@
         <v>73</v>
       </c>
       <c r="G202" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H202" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I202" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="J202" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="K202" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="L202" t="s">
-        <v>429</v>
+        <v>73</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A203" t="s">
-        <v>434</v>
+      <c r="A203" s="18" t="s">
+        <v>264</v>
       </c>
       <c r="B203" t="s">
-        <v>448</v>
+        <v>296</v>
       </c>
       <c r="C203" t="s">
-        <v>437</v>
+        <v>291</v>
       </c>
       <c r="D203">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="E203" t="s">
         <v>26</v>
@@ -12739,27 +12739,27 @@
         <v>73</v>
       </c>
       <c r="G203" t="s">
-        <v>263</v>
+        <v>73</v>
       </c>
       <c r="H203" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="I203" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="J203" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="K203" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="L203" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L203">
-    <sortCondition ref="D1:D203"/>
+    <sortCondition ref="C1:C203"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
